--- a/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
+++ b/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
@@ -574,7 +574,7 @@
     <t xml:space="preserve">Beta (own-stock weekly regression vs the Dubai index)</t>
   </si>
   <si>
-    <t xml:space="preserve">Own-stock weekly regression vs DFM General Index, full listing window 25-Nov-2022..17-Jul-2026 (3.64y, inside the 2-5y band): beta 0.652, R2 0.157, n 190, SE 0.110, CI90 [0.47, 0.83] — passes the usability gate (beta_result.json) (2026-08-09)</t>
+    <t xml:space="preserve">Own-stock weekly regression vs DFMGI (DFM General Index), 2022-11-25 to 2026-07-17 (3.64 years, 190 weeks): R-squared 0.16, standard error 0.11, 90% interval [0.47, 0.83] (2026-08-09)</t>
   </si>
   <si>
     <t xml:space="preserve">Marginal cost of debt</t>
@@ -4979,7 +4979,8 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5332,7 +5333,8 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
+++ b/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
@@ -955,7 +955,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Currency. AED million unless stated. Spot AED 1.50 (07-Aug-2026 close). Sheets: READ FIRST ·</t>
+          <t>Currency. AED million unless stated. Spot AED 1.57 (07-Aug-2026 close). Sheets: READ FIRST ·</t>
         </is>
       </c>
     </row>
@@ -2996,111 +2996,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>6.61%</t>
+          <t>6.64%</t>
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>2.036021037001202</v>
+        <v>2.028184513471483</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>2.278990030461237</v>
+        <v>2.268861693266772</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>2.503433676360321</v>
+        <v>2.491157603672834</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>2.573984217064922</v>
+        <v>2.561178372859041</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>2.647257998733412</v>
+        <v>2.633899818509498</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>7.11%</t>
+          <t>7.14%</t>
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>1.879971324219671</v>
+        <v>1.87319793838376</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>2.079646637493052</v>
+        <v>2.071104387653169</v>
       </c>
       <c r="D7" s="22" t="n">
-        <v>2.263741478972564</v>
+        <v>2.253560299465886</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>2.32406597281177</v>
+        <v>2.313456332733911</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>2.386679868385345</v>
+        <v>2.375623676455303</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>7.64%</t>
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>1.744457037324398</v>
+        <v>1.738544569942591</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>1.910445901115667</v>
+        <v>1.903144406851903</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>2.0634461375436</v>
+        <v>2.054867499874844</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>2.11544251909846</v>
+        <v>2.106512251969375</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>2.169378120712587</v>
+        <v>2.1600815122252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>8.11%</t>
+          <t>8.14%</t>
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>1.625681188180256</v>
+        <v>1.620475629041504</v>
       </c>
       <c r="C9" s="22" t="n">
-        <v>1.765032343705308</v>
+        <v>1.758719711547268</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>1.893600279280824</v>
+        <v>1.886274729863313</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>1.938722112390246</v>
+        <v>1.931104434285562</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>1.985496797450372</v>
+        <v>1.977574884837772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>8.61%</t>
+          <t>8.64%</t>
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>1.520728434623807</v>
+        <v>1.516110427892894</v>
       </c>
       <c r="C10" s="22" t="n">
-        <v>1.638719998912031</v>
+        <v>1.633208182647881</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>1.747772975135937</v>
+        <v>1.741445650749952</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>1.787155320306902</v>
+        <v>1.78058276703807</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>1.827953760844951</v>
+        <v>1.82112591758426</v>
       </c>
     </row>
     <row r="12">
@@ -7253,11 +7253,11 @@
         </is>
       </c>
       <c r="C5" s="22" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Uploaded DFM daily price history, last close (2026-08-07)</t>
+          <t>DFM close for EMPOWER, 3 September 2026, from the price file the principal supplied that day and committed to the repository. THE STUDY IS RE-STRUCK ON IT because no study is delivered against a stale price: the prior edition stood on the 7-August close of 1.50, and the stock has since risen 4.7% (2026-09-03)</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="C77" s="31" t="n">
-        <v>0.5000000000000012</v>
+        <v>0.4999999999999997</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>

--- a/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
+++ b/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
@@ -1236,23 +1236,23 @@
         <v>2512.224</v>
       </c>
       <c r="E9" s="28">
-        <f>(Assumptions!$C$80+Assumptions!$C$81)-E16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-E16</f>
         <v/>
       </c>
       <c r="F9" s="28">
-        <f>(Assumptions!$C$80+Assumptions!$C$81)-F16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-F16</f>
         <v/>
       </c>
       <c r="G9" s="28">
-        <f>(Assumptions!$C$80+Assumptions!$C$81)-G16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-G16</f>
         <v/>
       </c>
       <c r="H9" s="28">
-        <f>(Assumptions!$C$80+Assumptions!$C$81)-H16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-H16</f>
         <v/>
       </c>
       <c r="I9" s="28">
-        <f>(Assumptions!$C$80+Assumptions!$C$81)-I16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-I16</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
         <v>5503.717</v>
       </c>
       <c r="E11" s="28">
-        <f>Assumptions!$C$80+Assumptions!$C$81</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F11" s="28">
-        <f>Assumptions!$C$80+Assumptions!$C$81</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="G11" s="28">
-        <f>Assumptions!$C$80+Assumptions!$C$81</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="H11" s="28">
-        <f>Assumptions!$C$80+Assumptions!$C$81</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="I11" s="28">
-        <f>Assumptions!$C$80+Assumptions!$C$81</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -1389,27 +1389,27 @@
         <v/>
       </c>
       <c r="D13" s="33">
-        <f>Assumptions!$C$88</f>
+        <f>Assumptions!$C$93</f>
         <v/>
       </c>
       <c r="E13" s="33">
-        <f>$D13+Assumptions!$C$77*('Income Statement'!E18-Assumptions!$C$91)</f>
+        <f>$D13+Assumptions!$C$82*('Income Statement'!E18-Assumptions!$C$96)</f>
         <v/>
       </c>
       <c r="F13" s="33">
-        <f>E13+'Income Statement'!F18-Assumptions!$C$91</f>
+        <f>E13+'Income Statement'!F18-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="G13" s="33">
-        <f>F13+'Income Statement'!G18-Assumptions!$C$91</f>
+        <f>F13+'Income Statement'!G18-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="H13" s="33">
-        <f>G13+'Income Statement'!H18-Assumptions!$C$91</f>
+        <f>G13+'Income Statement'!H18-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="I13" s="33">
-        <f>H13+'Income Statement'!I18-Assumptions!$C$91</f>
+        <f>H13+'Income Statement'!I18-Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -1426,11 +1426,11 @@
         <v>186.378</v>
       </c>
       <c r="D14" s="19">
-        <f>Assumptions!$C$89</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="E14" s="28">
-        <f>$D14-Assumptions!$C$77*'Income Statement'!E17</f>
+        <f>$D14-Assumptions!$C$82*'Income Statement'!E17</f>
         <v/>
       </c>
       <c r="F14" s="28">
@@ -1510,23 +1510,23 @@
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>$D16-Assumptions!$C$77*(DCF!B18+('Income Statement'!E13+'Income Statement'!E6+'Income Statement'!E7)*(1-Assumptions!$C$7)-Assumptions!$C$91)</f>
+        <f>$D16-Assumptions!$C$82*(DCF!B18+('Income Statement'!E13+'Income Statement'!E6+'Income Statement'!E7)*(1-Assumptions!$C$7)-Assumptions!$C$96)</f>
         <v/>
       </c>
       <c r="F16" s="33">
-        <f>E16-(DCF!C18+('Income Statement'!F13+'Income Statement'!F6+'Income Statement'!F7)*(1-Assumptions!$C$7))+Assumptions!$C$91</f>
+        <f>E16-(DCF!C18+('Income Statement'!F13+'Income Statement'!F6+'Income Statement'!F7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="G16" s="33">
-        <f>F16-(DCF!D18+('Income Statement'!G13+'Income Statement'!G6+'Income Statement'!G7)*(1-Assumptions!$C$7))+Assumptions!$C$91</f>
+        <f>F16-(DCF!D18+('Income Statement'!G13+'Income Statement'!G6+'Income Statement'!G7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="H16" s="33">
-        <f>G16-(DCF!E18+('Income Statement'!H13+'Income Statement'!H6+'Income Statement'!H7)*(1-Assumptions!$C$7))+Assumptions!$C$91</f>
+        <f>G16-(DCF!E18+('Income Statement'!H13+'Income Statement'!H6+'Income Statement'!H7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="I16" s="33">
-        <f>H16-(DCF!F18+('Income Statement'!I13+'Income Statement'!I6+'Income Statement'!I7)*(1-Assumptions!$C$7))+Assumptions!$C$91</f>
+        <f>H16-(DCF!F18+('Income Statement'!I13+'Income Statement'!I6+'Income Statement'!I7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -2044,23 +2044,23 @@
         <v>-875</v>
       </c>
       <c r="D15" s="19">
-        <f>-Assumptions!$C$91</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="E15" s="19">
-        <f>-Assumptions!$C$91</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="F15" s="19">
-        <f>-Assumptions!$C$91</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="G15" s="19">
-        <f>-Assumptions!$C$91</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="H15" s="19">
-        <f>-Assumptions!$C$91</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
         <v>2.491157603672834</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>2.561178372859041</v>
+        <v>2.561178372859042</v>
       </c>
       <c r="F6" s="22" t="n">
         <v>2.633899818509498</v>
@@ -3097,7 +3097,7 @@
         <v>1.741445650749952</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>1.78058276703807</v>
+        <v>1.780582767038071</v>
       </c>
       <c r="F10" s="22" t="n">
         <v>1.82112591758426</v>
@@ -3126,7 +3126,7 @@
         <v>0.02</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.025</v>
+        <v>0.02499999999999991</v>
       </c>
       <c r="F13" s="24" t="n">
         <v>0.03</v>
@@ -3139,23 +3139,23 @@
         </is>
       </c>
       <c r="B14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-B13/DCF!$C$26)*((1+B13)/(1+DCF!$C$56))*(1-((1+B13)/(1+DCF!$C$56))^10)/(1-((1+B13)/(1+DCF!$C$56)))+DCF!$F$14*(1+B13)^10*(1+MIN(Assumptions!$C$76,B13))*(1-MIN(Assumptions!$C$76,B13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$76,B13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-B13/DCF!$C$26)*((1+B13)/(1+DCF!$C$56))*(1-((1+B13)/(1+DCF!$C$56))^10)/(1-((1+B13)/(1+DCF!$C$56)))+DCF!$F$14*(1+B13)^10*(1+MIN(Assumptions!$C$81,B13))*(1-MIN(Assumptions!$C$81,B13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,B13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-C13/DCF!$C$26)*((1+C13)/(1+DCF!$C$56))*(1-((1+C13)/(1+DCF!$C$56))^10)/(1-((1+C13)/(1+DCF!$C$56)))+DCF!$F$14*(1+C13)^10*(1+MIN(Assumptions!$C$76,C13))*(1-MIN(Assumptions!$C$76,C13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$76,C13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-C13/DCF!$C$26)*((1+C13)/(1+DCF!$C$56))*(1-((1+C13)/(1+DCF!$C$56))^10)/(1-((1+C13)/(1+DCF!$C$56)))+DCF!$F$14*(1+C13)^10*(1+MIN(Assumptions!$C$81,C13))*(1-MIN(Assumptions!$C$81,C13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,C13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-D13/DCF!$C$26)*((1+D13)/(1+DCF!$C$56))*(1-((1+D13)/(1+DCF!$C$56))^10)/(1-((1+D13)/(1+DCF!$C$56)))+DCF!$F$14*(1+D13)^10*(1+MIN(Assumptions!$C$76,D13))*(1-MIN(Assumptions!$C$76,D13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$76,D13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-D13/DCF!$C$26)*((1+D13)/(1+DCF!$C$56))*(1-((1+D13)/(1+DCF!$C$56))^10)/(1-((1+D13)/(1+DCF!$C$56)))+DCF!$F$14*(1+D13)^10*(1+MIN(Assumptions!$C$81,D13))*(1-MIN(Assumptions!$C$81,D13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,D13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-E13/DCF!$C$26)*((1+E13)/(1+DCF!$C$56))*(1-((1+E13)/(1+DCF!$C$56))^10)/(1-((1+E13)/(1+DCF!$C$56)))+DCF!$F$14*(1+E13)^10*(1+MIN(Assumptions!$C$76,E13))*(1-MIN(Assumptions!$C$76,E13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$76,E13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-E13/DCF!$C$26)*((1+E13)/(1+DCF!$C$56))*(1-((1+E13)/(1+DCF!$C$56))^10)/(1-((1+E13)/(1+DCF!$C$56)))+DCF!$F$14*(1+E13)^10*(1+MIN(Assumptions!$C$81,E13))*(1-MIN(Assumptions!$C$81,E13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,E13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-F13/DCF!$C$26)*((1+F13)/(1+DCF!$C$56))*(1-((1+F13)/(1+DCF!$C$56))^10)/(1-((1+F13)/(1+DCF!$C$56)))+DCF!$F$14*(1+F13)^10*(1+MIN(Assumptions!$C$76,F13))*(1-MIN(Assumptions!$C$76,F13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$76,F13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-F13/DCF!$C$26)*((1+F13)/(1+DCF!$C$56))*(1-((1+F13)/(1+DCF!$C$56))^10)/(1-((1+F13)/(1+DCF!$C$56)))+DCF!$F$14*(1+F13)^10*(1+MIN(Assumptions!$C$81,F13))*(1-MIN(Assumptions!$C$81,F13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,F13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -3616,23 +3616,23 @@
         </is>
       </c>
       <c r="B35" s="28">
-        <f>B30*Assumptions!$C$77/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>B30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>C30*Assumptions!$C$77/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>C30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="D35" s="28">
-        <f>D30*Assumptions!$C$77/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>D30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="E35" s="28">
-        <f>E30*Assumptions!$C$77/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>E30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="F35" s="28">
-        <f>F30*Assumptions!$C$77/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>F30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
     </row>
@@ -3801,27 +3801,27 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on capital</t>
-        </is>
-      </c>
-      <c r="B42" s="10">
-        <f>B41/(DCF!$F$11+Assumptions!$C$56*B24)</f>
-        <v/>
-      </c>
-      <c r="C42" s="10">
-        <f>C41/(DCF!$F$11+Assumptions!$C$56*C24)</f>
-        <v/>
-      </c>
-      <c r="D42" s="10">
-        <f>D41/(DCF!$F$11+Assumptions!$C$56*D24)</f>
-        <v/>
-      </c>
-      <c r="E42" s="10">
-        <f>E41/(DCF!$F$11+Assumptions!$C$56*E24)</f>
-        <v/>
-      </c>
-      <c r="F42" s="10">
-        <f>F41/(DCF!$F$11+Assumptions!$C$56*F24)</f>
+          <t>Stage-one free cash flow, FY2031 (the waterfall is on the DCF sheet)</t>
+        </is>
+      </c>
+      <c r="B42" s="28">
+        <f>1351.086349</f>
+        <v/>
+      </c>
+      <c r="C42" s="28">
+        <f>1374.204426</f>
+        <v/>
+      </c>
+      <c r="D42" s="28">
+        <f>1391.542984</f>
+        <v/>
+      </c>
+      <c r="E42" s="28">
+        <f>1408.881541</f>
+        <v/>
+      </c>
+      <c r="F42" s="28">
+        <f>1426.220099</f>
         <v/>
       </c>
     </row>
@@ -3832,23 +3832,23 @@
         </is>
       </c>
       <c r="B43" s="26">
-        <f>(1+Assumptions!$C$75)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="C43" s="26">
-        <f>(1+Assumptions!$C$75)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="D43" s="26">
-        <f>(1+Assumptions!$C$75)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="E43" s="26">
-        <f>(1+Assumptions!$C$75)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="F43" s="26">
-        <f>(1+Assumptions!$C$75)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
     </row>
@@ -3859,50 +3859,50 @@
         </is>
       </c>
       <c r="B44" s="28">
-        <f>B41*(1-Assumptions!$C$75/B42)*B43*(1-B43^10)/(1-B43)</f>
+        <f>B42/(1+DCF!$C$56)*(1-B43^10)/(1-B43)</f>
         <v/>
       </c>
       <c r="C44" s="28">
-        <f>C41*(1-Assumptions!$C$75/C42)*C43*(1-C43^10)/(1-C43)</f>
+        <f>C42/(1+DCF!$C$56)*(1-C43^10)/(1-C43)</f>
         <v/>
       </c>
       <c r="D44" s="28">
-        <f>D41*(1-Assumptions!$C$75/D42)*D43*(1-D43^10)/(1-D43)</f>
+        <f>D42/(1+DCF!$C$56)*(1-D43^10)/(1-D43)</f>
         <v/>
       </c>
       <c r="E44" s="28">
-        <f>E41*(1-Assumptions!$C$75/E42)*E43*(1-E43^10)/(1-E43)</f>
+        <f>E42/(1+DCF!$C$56)*(1-E43^10)/(1-E43)</f>
         <v/>
       </c>
       <c r="F44" s="28">
-        <f>F41*(1-Assumptions!$C$75/F42)*F43*(1-F43^10)/(1-F43)</f>
+        <f>F42/(1+DCF!$C$56)*(1-F43^10)/(1-F43)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>NOPAT in FY2040</t>
+          <t>Stage-two free cash flow, FY2041</t>
         </is>
       </c>
       <c r="B45" s="28">
-        <f>B41*(1+Assumptions!$C$75)^10</f>
+        <f>1747.758253</f>
         <v/>
       </c>
       <c r="C45" s="28">
-        <f>C41*(1+Assumptions!$C$75)^10</f>
+        <f>1776.747568</f>
         <v/>
       </c>
       <c r="D45" s="28">
-        <f>D41*(1+Assumptions!$C$75)^10</f>
+        <f>1798.489555</f>
         <v/>
       </c>
       <c r="E45" s="28">
-        <f>E41*(1+Assumptions!$C$75)^10</f>
+        <f>1820.231542</f>
         <v/>
       </c>
       <c r="F45" s="28">
-        <f>F41*(1+Assumptions!$C$75)^10</f>
+        <f>1841.973528</f>
         <v/>
       </c>
     </row>
@@ -3913,23 +3913,23 @@
         </is>
       </c>
       <c r="B46" s="28">
-        <f>B45*(1+Assumptions!$C$76)*(1-Assumptions!$C$76/B42)/((DCF!$C$56-Assumptions!$C$76)*(1+DCF!$C$56)^10)</f>
+        <f>B45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="C46" s="28">
-        <f>C45*(1+Assumptions!$C$76)*(1-Assumptions!$C$76/C42)/((DCF!$C$56-Assumptions!$C$76)*(1+DCF!$C$56)^10)</f>
+        <f>C45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="D46" s="28">
-        <f>D45*(1+Assumptions!$C$76)*(1-Assumptions!$C$76/D42)/((DCF!$C$56-Assumptions!$C$76)*(1+DCF!$C$56)^10)</f>
+        <f>D45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="E46" s="28">
-        <f>E45*(1+Assumptions!$C$76)*(1-Assumptions!$C$76/E42)/((DCF!$C$56-Assumptions!$C$76)*(1+DCF!$C$56)^10)</f>
+        <f>E45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="F46" s="28">
-        <f>F45*(1+Assumptions!$C$76)*(1-Assumptions!$C$76/F42)/((DCF!$C$56-Assumptions!$C$76)*(1+DCF!$C$56)^10)</f>
+        <f>F45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -4021,23 +4021,23 @@
         </is>
       </c>
       <c r="B50" s="34">
-        <f>(B49-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(B49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>(C49-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>(D49-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(D49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E50" s="34">
-        <f>(E49-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(E49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F50" s="34">
-        <f>(F49-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(F49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="C58" s="28">
-        <f>C53*Assumptions!$C$77/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>C53*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
     </row>
@@ -4183,11 +4183,11 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on capital (15%)</t>
-        </is>
-      </c>
-      <c r="C65" s="10">
-        <f>C64/(DCF!$F$11+Assumptions!$C$56*C24)</f>
+          <t>Stage-one free cash flow at 15% (the waterfall is on the DCF sheet)</t>
+        </is>
+      </c>
+      <c r="C65" s="28">
+        <f>1275.872653</f>
         <v/>
       </c>
     </row>
@@ -4198,18 +4198,18 @@
         </is>
       </c>
       <c r="C66" s="28">
-        <f>C64*(1-Assumptions!$C$75/C65)*C43*(1-C43^10)/(1-C43)</f>
+        <f>C65/(1+DCF!$C$56)*(1-C43^10)/(1-C43)</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>NOPAT in FY2040 (15%)</t>
+          <t>Stage-two free cash flow at 15%</t>
         </is>
       </c>
       <c r="C67" s="28">
-        <f>C64*(1+Assumptions!$C$75)^10</f>
+        <f>1652.102614</f>
         <v/>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="C68" s="28">
-        <f>C67*(1+Assumptions!$C$76)*(1-Assumptions!$C$76/C65)/((DCF!$C$56-Assumptions!$C$76)*(1+DCF!$C$56)^10)</f>
+        <f>C67*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="C72" s="16">
-        <f>(C71-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C71-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="B89" s="28">
-        <f>B88*Assumptions!$C$77/(1+$C$91)^DCF!$B$19</f>
+        <f>B88*Assumptions!$C$82/(1+$C$91)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C89" s="28">
@@ -4672,11 +4672,11 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on capital</t>
-        </is>
-      </c>
-      <c r="C94" s="10">
-        <f>C93/(F86+Assumptions!$C$56*F81)</f>
+          <t>Stage-one free cash flow, FY2031 (the waterfall is on the DCF sheet)</t>
+        </is>
+      </c>
+      <c r="C94" s="28">
+        <f>1086.112904</f>
         <v/>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C95" s="26">
-        <f>(1+Assumptions!$C$75)/(1+$C$91)</f>
+        <f>(1+Assumptions!$C$80)/(1+$C$91)</f>
         <v/>
       </c>
     </row>
@@ -4698,18 +4698,18 @@
         </is>
       </c>
       <c r="C96" s="28">
-        <f>C93*(1-Assumptions!$C$75/C94)*C95*(1-C95^10)/(1-C95)</f>
+        <f>C94/(1+$C$91)*(1-C95^10)/(1-C95)</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>NOPAT in FY2040</t>
+          <t>Stage-two free cash flow, FY2041</t>
         </is>
       </c>
       <c r="C97" s="28">
-        <f>C93*(1+Assumptions!$C$75)^10</f>
+        <f>1407.094633</f>
         <v/>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         </is>
       </c>
       <c r="C98" s="28">
-        <f>C97*(1+Assumptions!$C$76)*(1-Assumptions!$C$76/C94)/(($C$91-Assumptions!$C$76)*(1+$C$91)^10)</f>
+        <f>C97*(1+Assumptions!$C$81)/(($C$91-Assumptions!$C$81)*(1+$C$91)^10)</f>
         <v/>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B102" s="14" t="n"/>
       <c r="C102" s="34">
-        <f>(C101-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C101-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D102" s="14" t="n"/>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="B116" s="28">
-        <f>B115*Assumptions!$C$77/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>B115*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C116" s="28">
@@ -5123,11 +5123,11 @@
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on capital</t>
-        </is>
-      </c>
-      <c r="C119" s="10">
-        <f>C118/(F113+Assumptions!$C$56*F108)</f>
+          <t>Stage-one free cash flow, FY2031 (the waterfall is on the DCF sheet)</t>
+        </is>
+      </c>
+      <c r="C119" s="28">
+        <f>1443.493007</f>
         <v/>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="C120" s="26">
-        <f>(1+Assumptions!$C$75)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
     </row>
@@ -5149,18 +5149,18 @@
         </is>
       </c>
       <c r="C121" s="28">
-        <f>C118*(1-Assumptions!$C$75/C119)*C120*(1-C120^10)/(1-C120)</f>
+        <f>C119/(1+DCF!$C$56)*(1-C120^10)/(1-C120)</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>NOPAT in FY2040</t>
+          <t>Stage-two free cash flow, FY2041</t>
         </is>
       </c>
       <c r="C122" s="28">
-        <f>C118*(1+Assumptions!$C$75)^10</f>
+        <f>1865.103177</f>
         <v/>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="C123" s="28">
-        <f>C122*(1+Assumptions!$C$76)*(1-Assumptions!$C$76/C119)/((DCF!$C$56-Assumptions!$C$76)*(1+DCF!$C$56)^10)</f>
+        <f>C122*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B127" s="14" t="n"/>
       <c r="C127" s="34">
-        <f>(C126-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C126-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D127" s="14" t="n"/>
@@ -5274,15 +5274,15 @@
         </is>
       </c>
       <c r="B132" s="28">
-        <f>DCF!$B$18*Assumptions!$C$77/(1+B$131)^DCF!$B$19</f>
+        <f>DCF!$B$18*Assumptions!$C$82/(1+B$131)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C132" s="28">
-        <f>DCF!$B$18*Assumptions!$C$77/(1+C$131)^DCF!$B$19</f>
+        <f>DCF!$B$18*Assumptions!$C$82/(1+C$131)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="D132" s="28">
-        <f>DCF!$B$18*Assumptions!$C$77/(1+D$131)^DCF!$B$19</f>
+        <f>DCF!$B$18*Assumptions!$C$82/(1+D$131)^DCF!$B$19</f>
         <v/>
       </c>
     </row>
@@ -5388,15 +5388,15 @@
         </is>
       </c>
       <c r="B138" s="26">
-        <f>(1+Assumptions!$C$75)/(1+B131)</f>
+        <f>(1+Assumptions!$C$80)/(1+B131)</f>
         <v/>
       </c>
       <c r="C138" s="26">
-        <f>(1+Assumptions!$C$75)/(1+C131)</f>
+        <f>(1+Assumptions!$C$80)/(1+C131)</f>
         <v/>
       </c>
       <c r="D138" s="26">
-        <f>(1+Assumptions!$C$75)/(1+D131)</f>
+        <f>(1+Assumptions!$C$80)/(1+D131)</f>
         <v/>
       </c>
     </row>
@@ -5407,15 +5407,15 @@
         </is>
       </c>
       <c r="B139" s="28">
-        <f>DCF!$F$14*(1-DCF!$C$28)*B138*(1-B138^10)/(1-B138)</f>
+        <f>1408.881541/(1+B131)*(1-B138^10)/(1-B138)</f>
         <v/>
       </c>
       <c r="C139" s="28">
-        <f>DCF!$F$14*(1-DCF!$C$28)*C138*(1-C138^10)/(1-C138)</f>
+        <f>1408.881541/(1+C131)*(1-C138^10)/(1-C138)</f>
         <v/>
       </c>
       <c r="D139" s="28">
-        <f>DCF!$F$14*(1-DCF!$C$28)*D138*(1-D138^10)/(1-D138)</f>
+        <f>1408.881541/(1+D131)*(1-D138^10)/(1-D138)</f>
         <v/>
       </c>
     </row>
@@ -5426,15 +5426,15 @@
         </is>
       </c>
       <c r="B140" s="28">
-        <f>DCF!$C$33*(1+Assumptions!$C$76)*(1-DCF!$C$30)/((B131-Assumptions!$C$76)*(1+B131)^10)</f>
+        <f>1820.231542*(1+Assumptions!$C$81)/((B131-Assumptions!$C$81)*(1+B131)^10)</f>
         <v/>
       </c>
       <c r="C140" s="28">
-        <f>DCF!$C$33*(1+Assumptions!$C$76)*(1-DCF!$C$30)/((C131-Assumptions!$C$76)*(1+C131)^10)</f>
+        <f>1820.231542*(1+Assumptions!$C$81)/((C131-Assumptions!$C$81)*(1+C131)^10)</f>
         <v/>
       </c>
       <c r="D140" s="28">
-        <f>DCF!$C$33*(1+Assumptions!$C$76)*(1-DCF!$C$30)/((D131-Assumptions!$C$76)*(1+D131)^10)</f>
+        <f>1820.231542*(1+Assumptions!$C$81)/((D131-Assumptions!$C$81)*(1+D131)^10)</f>
         <v/>
       </c>
     </row>
@@ -5502,15 +5502,15 @@
         </is>
       </c>
       <c r="B144" s="34">
-        <f>(B143-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(B143-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C144" s="34">
-        <f>(C143-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C143-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D144" s="34">
-        <f>(D143-DCF!$C$53+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(D143-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5671,27 +5671,27 @@
         </is>
       </c>
       <c r="D6" s="9">
-        <f>Assumptions!$C$91/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>Assumptions!$C$91/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>Assumptions!$C$91/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="G6" s="9">
-        <f>Assumptions!$C$91/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="H6" s="9">
-        <f>Assumptions!$C$91/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="I6" s="9">
-        <f>Assumptions!$C$91/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5712,27 +5712,27 @@
         </is>
       </c>
       <c r="D7" s="39">
-        <f>'Income Statement'!D18/Assumptions!$C$91</f>
+        <f>'Income Statement'!D18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="E7" s="39">
-        <f>'Income Statement'!E18/Assumptions!$C$91</f>
+        <f>'Income Statement'!E18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="F7" s="39">
-        <f>'Income Statement'!F18/Assumptions!$C$91</f>
+        <f>'Income Statement'!F18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="G7" s="39">
-        <f>'Income Statement'!G18/Assumptions!$C$91</f>
+        <f>'Income Statement'!G18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="H7" s="39">
-        <f>'Income Statement'!H18/Assumptions!$C$91</f>
+        <f>'Income Statement'!H18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="I7" s="39">
-        <f>'Income Statement'!I18/Assumptions!$C$91</f>
+        <f>'Income Statement'!I18/Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -6118,27 +6118,27 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <f>Assumptions!$C$91/'Income Statement'!D18</f>
+        <f>Assumptions!$C$96/'Income Statement'!D18</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>Assumptions!$C$91/'Income Statement'!E18</f>
+        <f>Assumptions!$C$96/'Income Statement'!E18</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>Assumptions!$C$91/'Income Statement'!F18</f>
+        <f>Assumptions!$C$96/'Income Statement'!F18</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>Assumptions!$C$91/'Income Statement'!G18</f>
+        <f>Assumptions!$C$96/'Income Statement'!G18</f>
         <v/>
       </c>
       <c r="H17" s="10">
-        <f>Assumptions!$C$91/'Income Statement'!H18</f>
+        <f>Assumptions!$C$96/'Income Statement'!H18</f>
         <v/>
       </c>
       <c r="I17" s="10">
-        <f>Assumptions!$C$91/'Income Statement'!I18</f>
+        <f>Assumptions!$C$96/'Income Statement'!I18</f>
         <v/>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="B10" s="38">
-        <f>Assumptions!$C$94</f>
+        <f>Assumptions!$C$99</f>
         <v/>
       </c>
       <c r="C10" s="38">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="B11" s="38">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="C11" s="38">
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="B12" s="38">
-        <f>Assumptions!$C$96</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
       <c r="C12" s="38">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>Assumptions!$C$91/Assumptions!$C$6/Assumptions!$C$5</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
         <v/>
       </c>
       <c r="C5" s="8">
-        <f>Assumptions!$C$97</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="D5" s="9">
@@ -6487,7 +6487,7 @@
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$103</f>
         <v/>
       </c>
       <c r="D6" s="9">
@@ -6510,7 +6510,7 @@
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>Assumptions!$C$99</f>
+        <f>Assumptions!$C$104</f>
         <v/>
       </c>
       <c r="D7" s="9">
@@ -6533,7 +6533,7 @@
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>Assumptions!$C$100</f>
+        <f>Assumptions!$C$105</f>
         <v/>
       </c>
       <c r="D8" s="9">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>Assumptions!$C$97*Sensitivity!C50+Assumptions!$C$98*B6+Assumptions!$C$99*B7+Assumptions!$C$100*B8</f>
+        <f>Assumptions!$C$102*Sensitivity!C50+Assumptions!$C$103*B6+Assumptions!$C$104*B7+Assumptions!$C$105*B8</f>
         <v/>
       </c>
       <c r="E10" s="10">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>Assumptions!$C$97*'SOTP Bridge'!D14+Assumptions!$C$98*B6+Assumptions!$C$99*'Relative &amp; Normalized'!C34+Assumptions!$C$100*'Relative &amp; Normalized'!C41</f>
+        <f>Assumptions!$C$102*'SOTP Bridge'!D14+Assumptions!$C$103*B6+Assumptions!$C$104*'Relative &amp; Normalized'!C34+Assumptions!$C$105*'Relative &amp; Normalized'!C41</f>
         <v/>
       </c>
       <c r="E11" s="10">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>Assumptions!$C$97*Sensitivity!C72+Assumptions!$C$98*B6+Assumptions!$C$99*'Relative &amp; Normalized'!C34+Assumptions!$C$100*'Relative &amp; Normalized'!C41</f>
+        <f>Assumptions!$C$102*Sensitivity!C72+Assumptions!$C$103*B6+Assumptions!$C$104*'Relative &amp; Normalized'!C34+Assumptions!$C$105*'Relative &amp; Normalized'!C41</f>
         <v/>
       </c>
       <c r="E12" s="10">
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>Assumptions!$C$101</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="B34" s="8">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="B35" s="8">
-        <f>Assumptions!$C$76</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="C24" s="7">
-        <f>Assumptions!$C$101</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -8240,351 +8240,428 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Growth, FY2031-FY2040 window (stage one)</t>
-        </is>
-      </c>
-      <c r="C75" s="24" t="n">
-        <v>0.025</v>
+          <t>Terminal inflation — UAE house macro path</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="n">
+        <v>0.02</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth: long-run UAE nominal-GDP-consistent 2.5% under a flat regulated tariff — bounded by Dubai build-out saturation (connected 1.7m of ~2.0m RT contracted; sensitised 1.5-3.5%) (2026-08-09)</t>
+          <t>The house long-run inflation for this market; this study carries no inflation number of its own</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Growth beyond FY2040 (stage two, perpetuity)</t>
-        </is>
-      </c>
-      <c r="C76" s="24" t="n">
-        <v>0.015</v>
+          <t>REAL growth, FY2031-FY2040 window (stage one)</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="n">
+        <v>0.004901960784313725</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Long-run densification with ~zero real tariff growth under the RD10 no-indexation regime — the fade the Dubai-2040 build-out window decays to</t>
+          <t>Stage-one REAL growth, and it is the RESIDUE of a volume assumption rather than a rate anybody set: this company's tariff is REGULATED AND NOT INDEXED, so nominal revenue growth IS volume growth. The previous edition typed 2.5% nominal as the Dubai build-out rate (connected 1.7m of ~2.0m RT contracted), and on the house terminal inflation of 2.0% that is +0.49% real. STORING IT THIS WAY MOVES NO NUMBER HERE, which is the point worth recording: on a frozen-tariff business a typed nominal rate carries a meaning it does not carry elsewhere, and the storage rule makes that visible instead of leaving a reader to compute it (2026-08-09)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Stub period — 30-Jun-2026 anchor to end-FY2026 (years)</t>
-        </is>
-      </c>
-      <c r="C77" s="31" t="n">
-        <v>0.4999999999999997</v>
+          <t>REAL growth beyond FY2040 (stage two) — NEGATIVE</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="n">
+        <v>-0.004901960784313725</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>The bridge is struck on the 30-Jun-2026 reviewed balance sheet, so the cash-flow clock starts there too: FY2026 contributes its second half only and later year-ends sit at 1.5 to 4.5 years</t>
+          <t>Stage-two REAL growth, and it is NEGATIVE — written down as the real number it is rather than left inside a nominal 1.5%. The previous edition set stage two at 1.5% nominal for 'long-run densification with about zero real tariff growth', and against 2.0% inflation that is a real DECLINE of 0.49% a year for ever. Under a tariff the regulator does not index, a business whose volume grows more slowly than prices shrinks in real terms by construction, and this rate says so (2026-08-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Weighted asset life, DERIVED from notes 5, 6 and 7 (years)</t>
+        </is>
+      </c>
+      <c r="C78" s="25" t="n">
+        <v>28.09842122488282</v>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Audited consolidated financial statements for the year ended 31 December 2025, signed 9 February 2026, obtained from the company's own investor-relations page, notes 5, 6 and 7, DERIVED BY IDENTITY from those notes' own cost and charge columns and LABELLED as derived, and READ BY OCR OFF THE RENDERED PIXELS because the filing carries no usable text layer (85 bytes across 85 pages) and its property note is printed landscape, so the page was rotated before it could be read. ARITHMETIC IS THE ARBITER AND THE EXTRACTION FOOTS FOUR WAYS: the cost columns sum to the printed total of 10,929,327; the accumulated-depreciation columns to 3,734,337; cost less accumulated reproduces the balance sheet's 7,194,990; and the year's charge of 352,199 splits to the 341,696 in cost of sales and 10,503 in general and administrative expenses the notes state separately. Property, plant and equipment 10,001,105 (total less land, which is never depreciated, and less capital work in progress, whose accumulated column is impairment rather than depreciation) over 352,199 gives 28.40 years; right-of-use 22,649 over 5,361 gives 4.22; intangibles are DISCLOSED at 30 years outright and their gross cost follows from the flat charge. Blended, 28.10 years, cross-checked at 27.88 on FY2024's own columns. The right-of-use figure does NOT match the 15-year equipment lease the note names, and the note explains why rather than contradicting it: the book is 19,997 of buildings against 2,652 of equipment, and the buildings are a head office and labour accommodation on ONE-YEAR terms (2026-02-09)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>Bridge — 30-Jun-2026 reviewed balance sheet</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="n"/>
-      <c r="C79" s="14" t="n"/>
-      <c r="D79" s="14" t="n"/>
-      <c r="E79" s="14" t="n"/>
-      <c r="F79" s="14" t="n"/>
-      <c r="G79" s="14" t="n"/>
-      <c r="H79" s="14" t="n"/>
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Invested capital per unit of real growth (AED mn)</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="n">
+        <v>5526.341086457007</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>One per cent of real growth costs one per cent of the invested capital the business operates on. The marginal reading across the explicit window is NEGATIVE here, because the plant is written down faster than capex replaces it over those five years, and a negative capital requirement would credit this company for growing</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Bank borrowings (AED mn)</t>
-        </is>
-      </c>
-      <c r="C80" s="25" t="n">
-        <v>5502.845</v>
+          <t>Growth, FY2031-FY2040 window — (1+inflation)(1+real)-1</t>
+        </is>
+      </c>
+      <c r="C80" s="10">
+        <f>(1+$C$75)*(1+$C$76)-1</f>
+        <v/>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Bank borrowings 30-Jun-2026: current 2.845 + non-current 5,500.000, reviewed interim BS (2026-08-05)</t>
+          <t>DERIVED from the two rows above, never typed. It reproduces the previous edition's 2.50% to the basis point, because under a tariff the regulator does not index a nominal growth rate IS a volume assumption</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities (AED mn)</t>
-        </is>
-      </c>
-      <c r="C81" s="25" t="n">
-        <v>0.872</v>
+          <t>Growth beyond FY2040 — the same identity on the stage-two real rate</t>
+        </is>
+      </c>
+      <c r="C81" s="10">
+        <f>(1+$C$75)*(1+$C$77)-1</f>
+        <v/>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Lease liabilities 30-Jun-2026 (2026-08-05)</t>
+          <t>DERIVED. Reproduces the previous edition's 1.50%, and makes visible that it is a real DECLINE of half a point a year</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents (AED mn)</t>
-        </is>
-      </c>
-      <c r="C82" s="25" t="n">
-        <v>2472.012</v>
+          <t>Stub period — 30-Jun-2026 anchor to end-FY2026 (years)</t>
+        </is>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>0.4999999999999997</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents 30-Jun-2026 (2026-08-05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>Term deposits (AED mn)</t>
-        </is>
-      </c>
-      <c r="C83" s="25" t="n">
-        <v>40.212</v>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>Term deposits (&gt;3m) 30-Jun-2026 (2026-08-05)</t>
+          <t>The bridge is struck on the 30-Jun-2026 reviewed balance sheet, so the cash-flow clock starts there too: FY2026 contributes its second half only and later year-ends sit at 1.5 to 4.5 years</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>Related-party acquisition receivables at book (Note 8: 1,005.0 Dubai Aviation City + 289.4 Nakheel) (AED mn)</t>
-        </is>
-      </c>
-      <c r="C84" s="25" t="n">
-        <v>1294.442</v>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>Financial assets at amortised cost, 30-Jun-2026 reviewed BS: non-current 1,273.130 + current 21.312. Note 8 composition: AED 1,005.030 from Dubai Aviation City Corporation (DXB CoolCo acquisition, 2023) + AED 289.412 from Nakheel PJSC (Empower Snow acquisition, 2021) — related-party acquisition receivables under common control, NOT an operating concession asset. Clean financial-asset treatment adopted per critique (17-Aug-2026): interest income excluded from operating EBITDA/FCFF, asset added at book in the EV-to-equity bridge, and excluded from terminal invested capital (2026-08-05)</t>
-        </is>
-      </c>
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>Bridge — 30-Jun-2026 reviewed balance sheet</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="n"/>
+      <c r="C84" s="14" t="n"/>
+      <c r="D84" s="14" t="n"/>
+      <c r="E84" s="14" t="n"/>
+      <c r="F84" s="14" t="n"/>
+      <c r="G84" s="14" t="n"/>
+      <c r="H84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>Investment properties (AED mn)</t>
+          <t>Bank borrowings (AED mn)</t>
         </is>
       </c>
       <c r="C85" s="25" t="n">
-        <v>168.716</v>
+        <v>5502.845</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Investment properties 30-Jun-2026 (non-operating side pocket, added in the bridge at book) (2026-08-05)</t>
+          <t>Bank borrowings 30-Jun-2026: current 2.845 + non-current 5,500.000, reviewed interim BS (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at fair value through profit or loss (AED mn)</t>
+          <t>Lease liabilities (AED mn)</t>
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>53.411</v>
+        <v>0.872</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Financial assets at FVTPL 30-Jun-2026 (cash-like, added in the bridge) (2026-08-05)</t>
+          <t>Lease liabilities 30-Jun-2026 (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at fair value through OCI (AED mn)</t>
+          <t>Cash and cash equivalents (AED mn)</t>
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>74.56399999999999</v>
+        <v>2472.012</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Financial assets at FVOCI 30-Jun-2026 (added at book) (2026-08-05)</t>
+          <t>Cash and cash equivalents 30-Jun-2026 (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to shareholders, 30-Jun-2026 (AED mn)</t>
+          <t>Term deposits (AED mn)</t>
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>3337.585</v>
+        <v>40.212</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Equity attributable to holders, 30-Jun-2026 reviewed BS (2026-08-05)</t>
+          <t>Term deposits (&gt;3m) 30-Jun-2026 (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests, 30-Jun-2026 (AED mn)</t>
+          <t>Related-party acquisition receivables at book (Note 8: 1,005.0 Dubai Aviation City + 289.4 Nakheel) (AED mn)</t>
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>190.745</v>
+        <v>1294.442</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests (15% of DXB CoolCo et al. — the H1-2026 subsidiary note shows Dxb CoolCo FZCO at 85%/85%), 30-Jun-2026 reviewed BS (2026-08-05)</t>
+          <t>Financial assets at amortised cost, 30-Jun-2026 reviewed BS: non-current 1,273.130 + current 21.312. Note 8 composition: AED 1,005.030 from Dubai Aviation City Corporation (DXB CoolCo acquisition, 2023) + AED 289.412 from Nakheel PJSC (Empower Snow acquisition, 2021) — related-party acquisition receivables under common control, NOT an operating concession asset. Clean financial-asset treatment adopted per critique (17-Aug-2026): interest income excluded from operating EBITDA/FCFF, asset added at book in the EV-to-equity bridge, and excluded from terminal invested capital (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Yield earned on cash balances</t>
-        </is>
-      </c>
-      <c r="C90" s="30" t="n">
-        <v>0.03500000000000009</v>
+          <t>Investment properties (AED mn)</t>
+        </is>
+      </c>
+      <c r="C90" s="25" t="n">
+        <v>168.716</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Deposit-rate assumption used in the forecast finance line; flagged as an estimate</t>
+          <t>Investment properties 30-Jun-2026 (non-operating side pocket, added in the bridge at book) (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Committed annual dividend (AED mn)</t>
+          <t>Financial assets at fair value through profit or loss (AED mn)</t>
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>875</v>
+        <v>53.411</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Dividend AED 875m/yr committed for 2025 AND 2026 (2 x 437.5m, Oct/Apr), deck p12; FY2025 FS note 39: 875.0 paid in 2025 (2026-08-05)</t>
+          <t>Financial assets at FVTPL 30-Jun-2026 (cash-like, added in the bridge) (2026-08-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at fair value through OCI (AED mn)</t>
+        </is>
+      </c>
+      <c r="C92" s="25" t="n">
+        <v>74.56399999999999</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Financial assets at FVOCI 30-Jun-2026 (added at book) (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>Valuation lenses</t>
-        </is>
-      </c>
-      <c r="B93" s="14" t="n"/>
-      <c r="C93" s="14" t="n"/>
-      <c r="D93" s="14" t="n"/>
-      <c r="E93" s="14" t="n"/>
-      <c r="F93" s="14" t="n"/>
-      <c r="G93" s="14" t="n"/>
-      <c r="H93" s="14" t="n"/>
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Equity attributable to shareholders, 30-Jun-2026 (AED mn)</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="n">
+        <v>3337.585</v>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Equity attributable to holders, 30-Jun-2026 reviewed BS (2026-08-05)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Peer EV/EBITDA — Tabreed (trailing, restruck at the anchor)</t>
-        </is>
-      </c>
-      <c r="C94" s="32" t="n">
-        <v>10.1</v>
+          <t>Non-controlling interests, 30-Jun-2026 (AED mn)</t>
+        </is>
+      </c>
+      <c r="C94" s="25" t="n">
+        <v>190.745</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Tabreed (DFM) FY2025 results at the 2026-08-07 anchor (restruck: Tabreed 2.46 on 6/7-Aug; 0.5x of multiple = AED 0.078/share on this lens)</t>
+          <t>Non-controlling interests (15% of DXB CoolCo et al. — the H1-2026 subsidiary note shows Dxb CoolCo FZCO at 85%/85%), 30-Jun-2026 reviewed BS (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Peer price/earnings — Tabreed (trailing, restruck at the anchor)</t>
-        </is>
-      </c>
-      <c r="C95" s="32" t="n">
-        <v>15</v>
+          <t>Yield earned on cash balances</t>
+        </is>
+      </c>
+      <c r="C95" s="30" t="n">
+        <v>0.03500000000000009</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Tabreed (DFM), close 2.46 on 6/7-Aug-2026 — cross-check input only</t>
+          <t>Deposit-rate assumption used in the forecast finance line; flagged as an estimate</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Peer price/earnings — DEWA (parent)</t>
-        </is>
-      </c>
-      <c r="C96" s="32" t="n">
-        <v>16.8</v>
+          <t>Committed annual dividend (AED mn)</t>
+        </is>
+      </c>
+      <c r="C96" s="25" t="n">
+        <v>875</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>DEWA (DFM), Aug-2026 — context only, majority owner</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C97" s="24" t="n">
-        <v>0.5</v>
+          <t>Dividend AED 875m/yr committed for 2025 AND 2026 (2 x 437.5m, Oct/Apr), deck p12; FY2025 FS note 39: 875.0 paid in 2025 (2026-08-05)</t>
+        </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>Weight — relative multiples</t>
-        </is>
-      </c>
-      <c r="C98" s="24" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>Valuation lenses</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n"/>
+      <c r="C98" s="14" t="n"/>
+      <c r="D98" s="14" t="n"/>
+      <c r="E98" s="14" t="n"/>
+      <c r="F98" s="14" t="n"/>
+      <c r="G98" s="14" t="n"/>
+      <c r="H98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised earnings</t>
-        </is>
-      </c>
-      <c r="C99" s="24" t="n">
-        <v>0.15</v>
+          <t>Peer EV/EBITDA — Tabreed (trailing, restruck at the anchor)</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Tabreed (DFM) FY2025 results at the 2026-08-07 anchor (restruck: Tabreed 2.46 on 6/7-Aug; 0.5x of multiple = AED 0.078/share on this lens)</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Weight — book value</t>
-        </is>
-      </c>
-      <c r="C100" s="24" t="n">
-        <v>0.15</v>
+          <t>Peer price/earnings — Tabreed (trailing, restruck at the anchor)</t>
+        </is>
+      </c>
+      <c r="C100" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Tabreed (DFM), close 2.46 on 6/7-Aug-2026 — cross-check input only</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
+          <t>Peer price/earnings — DEWA (parent)</t>
+        </is>
+      </c>
+      <c r="C101" s="32" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>DEWA (DFM), Aug-2026 — context only, majority owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative multiples</t>
+        </is>
+      </c>
+      <c r="C103" s="24" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised earnings</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Weight — book value</t>
+        </is>
+      </c>
+      <c r="C105" s="24" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
           <t>DEWA control-transaction price, Feb-2026 (AED)</t>
         </is>
       </c>
-      <c r="C101" s="22" t="n">
+      <c r="C106" s="22" t="n">
         <v>2.16</v>
       </c>
-      <c r="H101" s="4" t="inlineStr">
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>Related-party CONTROL price for Dubai Holding's 24% stake — a disclosed reference point, never fair value</t>
         </is>
@@ -8669,7 +8746,7 @@
         <v/>
       </c>
       <c r="E5" s="19">
-        <f>DCF!C85</f>
+        <f>DCF!C86</f>
         <v/>
       </c>
     </row>
@@ -8699,15 +8776,15 @@
         </is>
       </c>
       <c r="C7" s="19">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="D7" s="19">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="E7" s="19">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -8718,15 +8795,15 @@
         </is>
       </c>
       <c r="C8" s="19">
-        <f>Assumptions!$C$85</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="D8" s="19">
-        <f>Assumptions!$C$85</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="E8" s="19">
-        <f>Assumptions!$C$85</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -8737,15 +8814,15 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$C$86</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
       <c r="D9" s="19">
-        <f>Assumptions!$C$86</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
       <c r="E9" s="19">
-        <f>Assumptions!$C$86</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
     </row>
@@ -8756,15 +8833,15 @@
         </is>
       </c>
       <c r="C10" s="19">
-        <f>Assumptions!$C$87</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="D10" s="19">
-        <f>Assumptions!$C$87</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="E10" s="19">
-        <f>Assumptions!$C$87</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -8872,7 +8949,7 @@
         <v/>
       </c>
       <c r="E16" s="8">
-        <f>DCF!C84/DCF!C85</f>
+        <f>DCF!C85/DCF!C86</f>
         <v/>
       </c>
     </row>
@@ -9688,7 +9765,7 @@
         </is>
       </c>
       <c r="C6" s="38">
-        <f>Assumptions!$C$94</f>
+        <f>Assumptions!$C$99</f>
         <v/>
       </c>
     </row>
@@ -9721,7 +9798,7 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -9732,7 +9809,7 @@
         </is>
       </c>
       <c r="C10" s="19">
-        <f>Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87</f>
+        <f>Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -9777,7 +9854,7 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>Assumptions!$C$95*'Income Statement'!E18/Assumptions!$C$6</f>
+        <f>Assumptions!$C$100*'Income Statement'!E18/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -9935,7 +10012,7 @@
         </is>
       </c>
       <c r="C30" s="38">
-        <f>(1-Assumptions!$C$75/C29)/(DCF!$C$50-Assumptions!$C$75)</f>
+        <f>(1-Assumptions!$C$80/C29)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -9969,7 +10046,7 @@
         </is>
       </c>
       <c r="C33" s="38">
-        <f>(1-Assumptions!$C$75/C32)/(DCF!$C$50-Assumptions!$C$75)</f>
+        <f>(1-Assumptions!$C$80/C32)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -10004,7 +10081,7 @@
         </is>
       </c>
       <c r="C37" s="9">
-        <f>Assumptions!$C$88/Assumptions!$C$6</f>
+        <f>Assumptions!$C$93/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -10015,7 +10092,7 @@
         </is>
       </c>
       <c r="C38" s="38">
-        <f>(C29-Assumptions!$C$75)/(DCF!$C$50-Assumptions!$C$75)</f>
+        <f>(C29-Assumptions!$C$80)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -10038,7 +10115,7 @@
         </is>
       </c>
       <c r="C40" s="38">
-        <f>(C32-Assumptions!$C$75)/(DCF!$C$50-Assumptions!$C$75)</f>
+        <f>(C32-Assumptions!$C$80)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -10073,7 +10150,7 @@
         </is>
       </c>
       <c r="C44" s="9">
-        <f>Assumptions!$C$91/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -10084,7 +10161,7 @@
         </is>
       </c>
       <c r="C45" s="7">
-        <f>C44*(1+Assumptions!$C$75)/(DCF!$C$50-Assumptions!$C$75)</f>
+        <f>C44*(1+Assumptions!$C$80)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -10106,7 +10183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -10558,7 +10635,7 @@
         </is>
       </c>
       <c r="B19" s="41">
-        <f>Assumptions!$C$77</f>
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C19" s="42">
@@ -10612,7 +10689,7 @@
         </is>
       </c>
       <c r="B21" s="43">
-        <f>B18*B20*Assumptions!$C$77</f>
+        <f>B18*B20*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C21" s="43">
@@ -10671,7 +10748,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
+          <t>Terminal return on invested capital (published; the terminal no longer uses it)</t>
         </is>
       </c>
       <c r="C26" s="10">
@@ -10686,40 +10763,40 @@
         </is>
       </c>
       <c r="C27" s="8">
-        <f>Assumptions!$C$75</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Stage-one reinvestment rate (growth / return on capital)</t>
-        </is>
-      </c>
-      <c r="C28" s="10">
-        <f>C27/C26</f>
+          <t>Stage-one free cash flow, FY2031 — the waterfall is at rows 93-101</t>
+        </is>
+      </c>
+      <c r="C28" s="28">
+        <f>C99</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Stage-two growth beyond FY2040 (long-run densification)</t>
+          <t>Stage-two growth beyond FY2040 (densification; a REAL decline)</t>
         </is>
       </c>
       <c r="C29" s="8">
-        <f>Assumptions!$C$76</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Stage-two reinvestment rate</t>
-        </is>
-      </c>
-      <c r="C30" s="10">
-        <f>C29/C26</f>
+          <t>Stage-two free cash flow, FY2041 — the waterfall is at rows 102-110</t>
+        </is>
+      </c>
+      <c r="C30" s="28">
+        <f>C108</f>
         <v/>
       </c>
     </row>
@@ -10741,18 +10818,18 @@
         </is>
       </c>
       <c r="C32" s="28">
-        <f>F14*(1-C28)*C31*(1-C31^10)/(1-C31)</f>
+        <f>C28/(1+$C$56)*(1-C31^10)/(1-C31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>NOPAT in FY2040 (year ten)</t>
-        </is>
-      </c>
-      <c r="C33" s="28">
-        <f>F14*(1+C27)^10</f>
+          <t>Stage-one free cash flow as a share of terminal profit</t>
+        </is>
+      </c>
+      <c r="C33" s="10">
+        <f>C28/(F14*(1+C27))</f>
         <v/>
       </c>
     </row>
@@ -10763,7 +10840,7 @@
         </is>
       </c>
       <c r="C34" s="28">
-        <f>C33*(1+C29)*(1-C30)/(($C$56-C29)*(1+$C$56)^10)</f>
+        <f>C30*(1+C29)/(($C$56-C29)*(1+$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -10979,7 +11056,7 @@
         </is>
       </c>
       <c r="C53" s="19">
-        <f>Assumptions!$C$80+Assumptions!$C$81-Assumptions!$C$82-Assumptions!$C$83</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86-Assumptions!$C$87-Assumptions!$C$88</f>
         <v/>
       </c>
     </row>
@@ -11114,7 +11191,7 @@
         </is>
       </c>
       <c r="B64" s="28">
-        <f>B63*B20*Assumptions!$C$77</f>
+        <f>B63*B20*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C64" s="28">
@@ -11148,7 +11225,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital (15%)</t>
+          <t>Terminal return on invested capital (15%; published, no longer used)</t>
         </is>
       </c>
       <c r="C66" s="10">
@@ -11159,22 +11236,22 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Stage-one reinvestment rate (15%)</t>
-        </is>
-      </c>
-      <c r="C67" s="10">
-        <f>C27/C66</f>
+          <t>Stage-one free cash flow at 15% — the waterfall is at rows 94-99</t>
+        </is>
+      </c>
+      <c r="C67" s="28">
+        <f>G99</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Stage-two reinvestment rate (15%)</t>
-        </is>
-      </c>
-      <c r="C68" s="10">
-        <f>C29/C66</f>
+          <t>Stage-two free cash flow at 15% — the waterfall is at rows 103-108</t>
+        </is>
+      </c>
+      <c r="C68" s="28">
+        <f>G108</f>
         <v/>
       </c>
     </row>
@@ -11185,18 +11262,18 @@
         </is>
       </c>
       <c r="C69" s="28">
-        <f>F62*(1-C67)*C31*(1-C31^10)/(1-C31)</f>
+        <f>C67/(1+$C$56)*(1-C31^10)/(1-C31)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>NOPAT in FY2040 (15%)</t>
-        </is>
-      </c>
-      <c r="C70" s="28">
-        <f>F62*(1+C27)^10</f>
+          <t>Stage-one free cash flow as a share of terminal profit (15%)</t>
+        </is>
+      </c>
+      <c r="C70" s="10">
+        <f>C67/(F62*(1+C27))</f>
         <v/>
       </c>
     </row>
@@ -11207,7 +11284,7 @@
         </is>
       </c>
       <c r="C71" s="28">
-        <f>C70*(1+C29)*(1-C68)/(($C$56-C29)*(1+$C$56)^10)</f>
+        <f>C68*(1+C29)/(($C$56-C29)*(1+$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -11269,7 +11346,7 @@
         </is>
       </c>
       <c r="B78" s="28">
-        <f>B18/(1+$D$56)^B19*Assumptions!$C$77</f>
+        <f>B18/(1+$D$56)^B19*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C78" s="28">
@@ -11314,65 +11391,76 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Value of the FY2031-40 window (CDS basis)</t>
+          <t>Stage-one free cash flow at the CDS-basis rate (its own maintenance charge)</t>
         </is>
       </c>
       <c r="C81" s="28">
-        <f>F14*(1-C28)*C80*(1-C80^10)/(1-C80)</f>
+        <f>1408.881541</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Value beyond FY2040 (CDS basis)</t>
+          <t>Value of the FY2031-40 window (CDS basis)</t>
         </is>
       </c>
       <c r="C82" s="28">
-        <f>C33*(1+C29)*(1-C30)/(($D$56-C29)*(1+$D$56)^10)</f>
+        <f>C81/(1+$D$56)*(1-C80^10)/(1-C80)</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Terminal value (CDS basis)</t>
+          <t>Value beyond FY2040 (CDS basis)</t>
         </is>
       </c>
       <c r="C83" s="28">
-        <f>C81+C82</f>
+        <f>1820.231542*(1+C29)/(($D$56-C29)*(1+$D$56)^10)</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>Present value of the terminal value (CDS basis)</t>
+          <t>Terminal value (CDS basis)</t>
         </is>
       </c>
       <c r="C84" s="28">
-        <f>C83/(1+$D$56)^F19</f>
+        <f>C82+C83</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>Enterprise value (CDS basis)</t>
-        </is>
-      </c>
-      <c r="C85" s="43">
-        <f>C79+C84</f>
+          <t>Present value of the terminal value (CDS basis)</t>
+        </is>
+      </c>
+      <c r="C85" s="28">
+        <f>C84/(1+$D$56)^F19</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
+          <t>Enterprise value (CDS basis)</t>
+        </is>
+      </c>
+      <c r="C86" s="43">
+        <f>C79+C85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
           <t>Fair value per share (CDS basis) — from the bridge</t>
         </is>
       </c>
-      <c r="C86" s="7">
+      <c r="C87" s="7">
         <f>'SOTP Bridge'!E14</f>
         <v/>
       </c>
@@ -11433,7 +11521,7 @@
         </is>
       </c>
       <c r="B91" s="27">
-        <f>(C52*C50+(Assumptions!$C$80+Assumptions!$C$81)*C51*(1-Assumptions!$C$7))/(C52+Assumptions!$C$80+Assumptions!$C$81)</f>
+        <f>(C52*C50+(Assumptions!$C$85+Assumptions!$C$86)*C51*(1-Assumptions!$C$7))/(C52+Assumptions!$C$85+Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="C91" s="7">
@@ -11453,7 +11541,7 @@
         </is>
       </c>
       <c r="B92" s="27">
-        <f>C55*C50+C54*(((Assumptions!$C$80+Assumptions!$C$81)*C51*(1-Assumptions!$C$7)-(Assumptions!$C$82+Assumptions!$C$83)*Assumptions!$C$90*(1-Assumptions!$C$7))/C53)</f>
+        <f>C55*C50+C54*(((Assumptions!$C$85+Assumptions!$C$86)*C51*(1-Assumptions!$C$7)-(Assumptions!$C$87+Assumptions!$C$88)*Assumptions!$C$95*(1-Assumptions!$C$7))/C53)</f>
         <v/>
       </c>
       <c r="C92" s="7">
@@ -11484,6 +11572,197 @@
         <is>
           <t>The listing exchange's own index gives beta 0.652; the FTSE ADX base-market regression (0.863) is primary per the house market definition.</t>
         </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Stage one, FY2031 — operating profit after tax, grown one year</t>
+        </is>
+      </c>
+      <c r="C94" s="28">
+        <f>1486.936920*(1+0.0250000000)</f>
+        <v/>
+      </c>
+      <c r="G94" s="28">
+        <f>1388.897123*(1+0.0250000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Stage one, FY2031 — plus the book depreciation and amortisation charge, grown</t>
+        </is>
+      </c>
+      <c r="C95" s="28">
+        <f>408.390760*(1+0.0250000000)</f>
+        <v/>
+      </c>
+      <c r="G95" s="28">
+        <f>408.390760*(1+0.0250000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Stage one, FY2031 — less capital maintenance at replacement cost, that charge escalated over half the derived life</t>
+        </is>
+      </c>
+      <c r="C96" s="28">
+        <f>-C95*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
+        <v/>
+      </c>
+      <c r="G96" s="28">
+        <f>-G95*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Stage one, FY2031 — less the capital real growth consumes</t>
+        </is>
+      </c>
+      <c r="C97" s="28">
+        <f>-0.0049019608*5526.341086</f>
+        <v/>
+      </c>
+      <c r="G97" s="28">
+        <f>-0.0049019608*5526.341086</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>Stage one, FY2031 — less inflation on working capital (a CREDIT here: this company is funded by its own customers)</t>
+        </is>
+      </c>
+      <c r="C98" s="28">
+        <f>-Assumptions!$C$75*-2250.419341*(1+0.0250000000)</f>
+        <v/>
+      </c>
+      <c r="G98" s="28">
+        <f>-Assumptions!$C$75*-2250.419341*(1+0.0250000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Stage one, FY2031 — FREE CASH FLOW</t>
+        </is>
+      </c>
+      <c r="C99" s="43">
+        <f>SUM(C94:C98)</f>
+        <v/>
+      </c>
+      <c r="G99" s="43">
+        <f>SUM(G94:G98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Stage two, FY2041 — operating profit after tax, grown one year</t>
+        </is>
+      </c>
+      <c r="C103" s="28">
+        <f>1903.404970*(1+0.0150000000)</f>
+        <v/>
+      </c>
+      <c r="G103" s="28">
+        <f>1777.905741*(1+0.0150000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Stage two, FY2041 — plus the book depreciation and amortisation charge, grown</t>
+        </is>
+      </c>
+      <c r="C104" s="28">
+        <f>522.774699*(1+0.0150000000)</f>
+        <v/>
+      </c>
+      <c r="G104" s="28">
+        <f>522.774699*(1+0.0150000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Stage two, FY2041 — less capital maintenance at replacement cost, that charge escalated over half the derived life</t>
+        </is>
+      </c>
+      <c r="C105" s="28">
+        <f>-C104*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
+        <v/>
+      </c>
+      <c r="G105" s="28">
+        <f>-G104*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Stage two, FY2041 — less the capital real growth consumes</t>
+        </is>
+      </c>
+      <c r="C106" s="28">
+        <f>--0.0049019608*0.000000</f>
+        <v/>
+      </c>
+      <c r="G106" s="28">
+        <f>--0.0049019608*0.000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Stage two, FY2041 — less inflation on working capital (a CREDIT here: this company is funded by its own customers)</t>
+        </is>
+      </c>
+      <c r="C107" s="28">
+        <f>-Assumptions!$C$75*-2880.727016*(1+0.0150000000)</f>
+        <v/>
+      </c>
+      <c r="G107" s="28">
+        <f>-Assumptions!$C$75*-2880.727016*(1+0.0150000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Stage two, FY2041 — FREE CASH FLOW</t>
+        </is>
+      </c>
+      <c r="C108" s="43">
+        <f>SUM(C103:C107)</f>
+        <v/>
+      </c>
+      <c r="G108" s="43">
+        <f>SUM(G103:G107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>Memo — the no-growth perpetuity at book depreciation, a diagnostic and not a bound</t>
+        </is>
+      </c>
+      <c r="C111" s="28">
+        <f>F14*(1+C27)/$C$56</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -11906,23 +12185,23 @@
         <v/>
       </c>
       <c r="E13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$80-Assumptions!$C$90*Assumptions!$C$82)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*Assumptions!$C$87)</f>
         <v/>
       </c>
       <c r="F13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$80-Assumptions!$C$90*'Balance Sheet'!E9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!E9)</f>
         <v/>
       </c>
       <c r="G13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$80-Assumptions!$C$90*'Balance Sheet'!F9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!F9)</f>
         <v/>
       </c>
       <c r="H13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$80-Assumptions!$C$90*'Balance Sheet'!G9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!G9)</f>
         <v/>
       </c>
       <c r="I13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$80-Assumptions!$C$90*'Balance Sheet'!H9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!H9)</f>
         <v/>
       </c>
     </row>

--- a/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
+++ b/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
@@ -1236,23 +1236,23 @@
         <v>2512.224</v>
       </c>
       <c r="E9" s="28">
-        <f>(Assumptions!$C$85+Assumptions!$C$86)-E16</f>
+        <f>(Assumptions!$C$86+Assumptions!$C$87)-E16</f>
         <v/>
       </c>
       <c r="F9" s="28">
-        <f>(Assumptions!$C$85+Assumptions!$C$86)-F16</f>
+        <f>(Assumptions!$C$86+Assumptions!$C$87)-F16</f>
         <v/>
       </c>
       <c r="G9" s="28">
-        <f>(Assumptions!$C$85+Assumptions!$C$86)-G16</f>
+        <f>(Assumptions!$C$86+Assumptions!$C$87)-G16</f>
         <v/>
       </c>
       <c r="H9" s="28">
-        <f>(Assumptions!$C$85+Assumptions!$C$86)-H16</f>
+        <f>(Assumptions!$C$86+Assumptions!$C$87)-H16</f>
         <v/>
       </c>
       <c r="I9" s="28">
-        <f>(Assumptions!$C$85+Assumptions!$C$86)-I16</f>
+        <f>(Assumptions!$C$86+Assumptions!$C$87)-I16</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
         <v>5503.717</v>
       </c>
       <c r="E11" s="28">
-        <f>Assumptions!$C$85+Assumptions!$C$86</f>
+        <f>Assumptions!$C$86+Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="F11" s="28">
-        <f>Assumptions!$C$85+Assumptions!$C$86</f>
+        <f>Assumptions!$C$86+Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="G11" s="28">
-        <f>Assumptions!$C$85+Assumptions!$C$86</f>
+        <f>Assumptions!$C$86+Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="H11" s="28">
-        <f>Assumptions!$C$85+Assumptions!$C$86</f>
+        <f>Assumptions!$C$86+Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="I11" s="28">
-        <f>Assumptions!$C$85+Assumptions!$C$86</f>
+        <f>Assumptions!$C$86+Assumptions!$C$87</f>
         <v/>
       </c>
     </row>
@@ -1389,27 +1389,27 @@
         <v/>
       </c>
       <c r="D13" s="33">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="E13" s="33">
-        <f>$D13+Assumptions!$C$82*('Income Statement'!E18-Assumptions!$C$96)</f>
+        <f>$D13+Assumptions!$C$83*('Income Statement'!E18-Assumptions!$C$97)</f>
         <v/>
       </c>
       <c r="F13" s="33">
-        <f>E13+'Income Statement'!F18-Assumptions!$C$96</f>
+        <f>E13+'Income Statement'!F18-Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="G13" s="33">
-        <f>F13+'Income Statement'!G18-Assumptions!$C$96</f>
+        <f>F13+'Income Statement'!G18-Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="H13" s="33">
-        <f>G13+'Income Statement'!H18-Assumptions!$C$96</f>
+        <f>G13+'Income Statement'!H18-Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="I13" s="33">
-        <f>H13+'Income Statement'!I18-Assumptions!$C$96</f>
+        <f>H13+'Income Statement'!I18-Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -1426,11 +1426,11 @@
         <v>186.378</v>
       </c>
       <c r="D14" s="19">
-        <f>Assumptions!$C$94</f>
+        <f>Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="E14" s="28">
-        <f>$D14-Assumptions!$C$82*'Income Statement'!E17</f>
+        <f>$D14-Assumptions!$C$83*'Income Statement'!E17</f>
         <v/>
       </c>
       <c r="F14" s="28">
@@ -1510,23 +1510,23 @@
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>$D16-Assumptions!$C$82*(DCF!B18+('Income Statement'!E13+'Income Statement'!E6+'Income Statement'!E7)*(1-Assumptions!$C$7)-Assumptions!$C$96)</f>
+        <f>$D16-Assumptions!$C$83*(DCF!B18+('Income Statement'!E13+'Income Statement'!E6+'Income Statement'!E7)*(1-Assumptions!$C$7)-Assumptions!$C$97)</f>
         <v/>
       </c>
       <c r="F16" s="33">
-        <f>E16-(DCF!C18+('Income Statement'!F13+'Income Statement'!F6+'Income Statement'!F7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
+        <f>E16-(DCF!C18+('Income Statement'!F13+'Income Statement'!F6+'Income Statement'!F7)*(1-Assumptions!$C$7))+Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="G16" s="33">
-        <f>F16-(DCF!D18+('Income Statement'!G13+'Income Statement'!G6+'Income Statement'!G7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
+        <f>F16-(DCF!D18+('Income Statement'!G13+'Income Statement'!G6+'Income Statement'!G7)*(1-Assumptions!$C$7))+Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="H16" s="33">
-        <f>G16-(DCF!E18+('Income Statement'!H13+'Income Statement'!H6+'Income Statement'!H7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
+        <f>G16-(DCF!E18+('Income Statement'!H13+'Income Statement'!H6+'Income Statement'!H7)*(1-Assumptions!$C$7))+Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="I16" s="33">
-        <f>H16-(DCF!F18+('Income Statement'!I13+'Income Statement'!I6+'Income Statement'!I7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
+        <f>H16-(DCF!F18+('Income Statement'!I13+'Income Statement'!I6+'Income Statement'!I7)*(1-Assumptions!$C$7))+Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -2044,23 +2044,23 @@
         <v>-875</v>
       </c>
       <c r="D15" s="19">
-        <f>-Assumptions!$C$96</f>
+        <f>-Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="E15" s="19">
-        <f>-Assumptions!$C$96</f>
+        <f>-Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="F15" s="19">
-        <f>-Assumptions!$C$96</f>
+        <f>-Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="G15" s="19">
-        <f>-Assumptions!$C$96</f>
+        <f>-Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="H15" s="19">
-        <f>-Assumptions!$C$96</f>
+        <f>-Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -3139,23 +3139,23 @@
         </is>
       </c>
       <c r="B14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-B13/DCF!$C$26)*((1+B13)/(1+DCF!$C$56))*(1-((1+B13)/(1+DCF!$C$56))^10)/(1-((1+B13)/(1+DCF!$C$56)))+DCF!$F$14*(1+B13)^10*(1+MIN(Assumptions!$C$81,B13))*(1-MIN(Assumptions!$C$81,B13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,B13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-B13/DCF!$C$26)*((1+B13)/(1+DCF!$C$56))*(1-((1+B13)/(1+DCF!$C$56))^10)/(1-((1+B13)/(1+DCF!$C$56)))+DCF!$F$14*(1+B13)^10*(1+MIN(Assumptions!$C$82,B13))*(1-MIN(Assumptions!$C$82,B13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,B13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-C13/DCF!$C$26)*((1+C13)/(1+DCF!$C$56))*(1-((1+C13)/(1+DCF!$C$56))^10)/(1-((1+C13)/(1+DCF!$C$56)))+DCF!$F$14*(1+C13)^10*(1+MIN(Assumptions!$C$81,C13))*(1-MIN(Assumptions!$C$81,C13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,C13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-C13/DCF!$C$26)*((1+C13)/(1+DCF!$C$56))*(1-((1+C13)/(1+DCF!$C$56))^10)/(1-((1+C13)/(1+DCF!$C$56)))+DCF!$F$14*(1+C13)^10*(1+MIN(Assumptions!$C$82,C13))*(1-MIN(Assumptions!$C$82,C13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,C13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-D13/DCF!$C$26)*((1+D13)/(1+DCF!$C$56))*(1-((1+D13)/(1+DCF!$C$56))^10)/(1-((1+D13)/(1+DCF!$C$56)))+DCF!$F$14*(1+D13)^10*(1+MIN(Assumptions!$C$81,D13))*(1-MIN(Assumptions!$C$81,D13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,D13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-D13/DCF!$C$26)*((1+D13)/(1+DCF!$C$56))*(1-((1+D13)/(1+DCF!$C$56))^10)/(1-((1+D13)/(1+DCF!$C$56)))+DCF!$F$14*(1+D13)^10*(1+MIN(Assumptions!$C$82,D13))*(1-MIN(Assumptions!$C$82,D13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,D13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-E13/DCF!$C$26)*((1+E13)/(1+DCF!$C$56))*(1-((1+E13)/(1+DCF!$C$56))^10)/(1-((1+E13)/(1+DCF!$C$56)))+DCF!$F$14*(1+E13)^10*(1+MIN(Assumptions!$C$81,E13))*(1-MIN(Assumptions!$C$81,E13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,E13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-E13/DCF!$C$26)*((1+E13)/(1+DCF!$C$56))*(1-((1+E13)/(1+DCF!$C$56))^10)/(1-((1+E13)/(1+DCF!$C$56)))+DCF!$F$14*(1+E13)^10*(1+MIN(Assumptions!$C$82,E13))*(1-MIN(Assumptions!$C$82,E13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,E13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-F13/DCF!$C$26)*((1+F13)/(1+DCF!$C$56))*(1-((1+F13)/(1+DCF!$C$56))^10)/(1-((1+F13)/(1+DCF!$C$56)))+DCF!$F$14*(1+F13)^10*(1+MIN(Assumptions!$C$81,F13))*(1-MIN(Assumptions!$C$81,F13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,F13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-F13/DCF!$C$26)*((1+F13)/(1+DCF!$C$56))*(1-((1+F13)/(1+DCF!$C$56))^10)/(1-((1+F13)/(1+DCF!$C$56)))+DCF!$F$14*(1+F13)^10*(1+MIN(Assumptions!$C$82,F13))*(1-MIN(Assumptions!$C$82,F13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,F13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -3616,23 +3616,23 @@
         </is>
       </c>
       <c r="B35" s="28">
-        <f>B30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>B30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>C30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>C30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="D35" s="28">
-        <f>D30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>D30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="E35" s="28">
-        <f>E30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>E30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="F35" s="28">
-        <f>F30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>F30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
     </row>
@@ -3805,23 +3805,23 @@
         </is>
       </c>
       <c r="B42" s="28">
-        <f>1351.086349</f>
+        <f>1390.755402</f>
         <v/>
       </c>
       <c r="C42" s="28">
-        <f>1374.204426</f>
+        <f>1413.873478</f>
         <v/>
       </c>
       <c r="D42" s="28">
-        <f>1391.542984</f>
+        <f>1431.212036</f>
         <v/>
       </c>
       <c r="E42" s="28">
-        <f>1408.881541</f>
+        <f>1448.550594</f>
         <v/>
       </c>
       <c r="F42" s="28">
-        <f>1426.220099</f>
+        <f>1465.889151</f>
         <v/>
       </c>
     </row>
@@ -3832,23 +3832,23 @@
         </is>
       </c>
       <c r="B43" s="26">
-        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="C43" s="26">
-        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="D43" s="26">
-        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="E43" s="26">
-        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="F43" s="26">
-        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
         <v/>
       </c>
     </row>
@@ -3886,23 +3886,23 @@
         </is>
       </c>
       <c r="B45" s="28">
-        <f>1747.758253</f>
+        <f>1798.042581</f>
         <v/>
       </c>
       <c r="C45" s="28">
-        <f>1776.747568</f>
+        <f>1827.031897</f>
         <v/>
       </c>
       <c r="D45" s="28">
-        <f>1798.489555</f>
+        <f>1848.773883</f>
         <v/>
       </c>
       <c r="E45" s="28">
-        <f>1820.231542</f>
+        <f>1870.515870</f>
         <v/>
       </c>
       <c r="F45" s="28">
-        <f>1841.973528</f>
+        <f>1892.257857</f>
         <v/>
       </c>
     </row>
@@ -3913,23 +3913,23 @@
         </is>
       </c>
       <c r="B46" s="28">
-        <f>B45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
+        <f>B45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="C46" s="28">
-        <f>C45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
+        <f>C45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="D46" s="28">
-        <f>D45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
+        <f>D45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="E46" s="28">
-        <f>E45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
+        <f>E45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="F46" s="28">
-        <f>F45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
+        <f>F45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -4021,23 +4021,23 @@
         </is>
       </c>
       <c r="B50" s="34">
-        <f>(B49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(B49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>(C49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>(D49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(D49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E50" s="34">
-        <f>(E49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(E49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F50" s="34">
-        <f>(F49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(F49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="C58" s="28">
-        <f>C53*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>C53*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="C65" s="28">
-        <f>1275.872653</f>
+        <f>1315.541705</f>
         <v/>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="C67" s="28">
-        <f>1652.102614</f>
+        <f>1702.386943</f>
         <v/>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="C68" s="28">
-        <f>C67*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
+        <f>C67*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="C72" s="16">
-        <f>(C71-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C71-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="B89" s="28">
-        <f>B88*Assumptions!$C$82/(1+$C$91)^DCF!$B$19</f>
+        <f>B88*Assumptions!$C$83/(1+$C$91)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C89" s="28">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="C94" s="28">
-        <f>1086.112904</f>
+        <f>1121.543485</f>
         <v/>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C95" s="26">
-        <f>(1+Assumptions!$C$80)/(1+$C$91)</f>
+        <f>(1+Assumptions!$C$81)/(1+$C$91)</f>
         <v/>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C97" s="28">
-        <f>1407.094633</f>
+        <f>1452.006293</f>
         <v/>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         </is>
       </c>
       <c r="C98" s="28">
-        <f>C97*(1+Assumptions!$C$81)/(($C$91-Assumptions!$C$81)*(1+$C$91)^10)</f>
+        <f>C97*(1+Assumptions!$C$82)/(($C$91-Assumptions!$C$82)*(1+$C$91)^10)</f>
         <v/>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B102" s="14" t="n"/>
       <c r="C102" s="34">
-        <f>(C101-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C101-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D102" s="14" t="n"/>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="B116" s="28">
-        <f>B115*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>B115*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C116" s="28">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="C119" s="28">
-        <f>1443.493007</f>
+        <f>1483.954471</f>
         <v/>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="C120" s="26">
-        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
         <v/>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="C122" s="28">
-        <f>1865.103177</f>
+        <f>1916.391964</f>
         <v/>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="C123" s="28">
-        <f>C122*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
+        <f>C122*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B127" s="14" t="n"/>
       <c r="C127" s="34">
-        <f>(C126-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C126-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D127" s="14" t="n"/>
@@ -5274,15 +5274,15 @@
         </is>
       </c>
       <c r="B132" s="28">
-        <f>DCF!$B$18*Assumptions!$C$82/(1+B$131)^DCF!$B$19</f>
+        <f>DCF!$B$18*Assumptions!$C$83/(1+B$131)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C132" s="28">
-        <f>DCF!$B$18*Assumptions!$C$82/(1+C$131)^DCF!$B$19</f>
+        <f>DCF!$B$18*Assumptions!$C$83/(1+C$131)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="D132" s="28">
-        <f>DCF!$B$18*Assumptions!$C$82/(1+D$131)^DCF!$B$19</f>
+        <f>DCF!$B$18*Assumptions!$C$83/(1+D$131)^DCF!$B$19</f>
         <v/>
       </c>
     </row>
@@ -5388,15 +5388,15 @@
         </is>
       </c>
       <c r="B138" s="26">
-        <f>(1+Assumptions!$C$80)/(1+B131)</f>
+        <f>(1+Assumptions!$C$81)/(1+B131)</f>
         <v/>
       </c>
       <c r="C138" s="26">
-        <f>(1+Assumptions!$C$80)/(1+C131)</f>
+        <f>(1+Assumptions!$C$81)/(1+C131)</f>
         <v/>
       </c>
       <c r="D138" s="26">
-        <f>(1+Assumptions!$C$80)/(1+D131)</f>
+        <f>(1+Assumptions!$C$81)/(1+D131)</f>
         <v/>
       </c>
     </row>
@@ -5407,15 +5407,15 @@
         </is>
       </c>
       <c r="B139" s="28">
-        <f>1408.881541/(1+B131)*(1-B138^10)/(1-B138)</f>
+        <f>1448.550594/(1+B131)*(1-B138^10)/(1-B138)</f>
         <v/>
       </c>
       <c r="C139" s="28">
-        <f>1408.881541/(1+C131)*(1-C138^10)/(1-C138)</f>
+        <f>1448.550594/(1+C131)*(1-C138^10)/(1-C138)</f>
         <v/>
       </c>
       <c r="D139" s="28">
-        <f>1408.881541/(1+D131)*(1-D138^10)/(1-D138)</f>
+        <f>1448.550594/(1+D131)*(1-D138^10)/(1-D138)</f>
         <v/>
       </c>
     </row>
@@ -5426,15 +5426,15 @@
         </is>
       </c>
       <c r="B140" s="28">
-        <f>1820.231542*(1+Assumptions!$C$81)/((B131-Assumptions!$C$81)*(1+B131)^10)</f>
+        <f>1870.515870*(1+Assumptions!$C$82)/((B131-Assumptions!$C$82)*(1+B131)^10)</f>
         <v/>
       </c>
       <c r="C140" s="28">
-        <f>1820.231542*(1+Assumptions!$C$81)/((C131-Assumptions!$C$81)*(1+C131)^10)</f>
+        <f>1870.515870*(1+Assumptions!$C$82)/((C131-Assumptions!$C$82)*(1+C131)^10)</f>
         <v/>
       </c>
       <c r="D140" s="28">
-        <f>1820.231542*(1+Assumptions!$C$81)/((D131-Assumptions!$C$81)*(1+D131)^10)</f>
+        <f>1870.515870*(1+Assumptions!$C$82)/((D131-Assumptions!$C$82)*(1+D131)^10)</f>
         <v/>
       </c>
     </row>
@@ -5502,15 +5502,15 @@
         </is>
       </c>
       <c r="B144" s="34">
-        <f>(B143-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(B143-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C144" s="34">
-        <f>(C143-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C143-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D144" s="34">
-        <f>(D143-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(D143-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5671,27 +5671,27 @@
         </is>
       </c>
       <c r="D6" s="9">
-        <f>Assumptions!$C$96/Assumptions!$C$6</f>
+        <f>Assumptions!$C$97/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>Assumptions!$C$96/Assumptions!$C$6</f>
+        <f>Assumptions!$C$97/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>Assumptions!$C$96/Assumptions!$C$6</f>
+        <f>Assumptions!$C$97/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="G6" s="9">
-        <f>Assumptions!$C$96/Assumptions!$C$6</f>
+        <f>Assumptions!$C$97/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="H6" s="9">
-        <f>Assumptions!$C$96/Assumptions!$C$6</f>
+        <f>Assumptions!$C$97/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="I6" s="9">
-        <f>Assumptions!$C$96/Assumptions!$C$6</f>
+        <f>Assumptions!$C$97/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5712,27 +5712,27 @@
         </is>
       </c>
       <c r="D7" s="39">
-        <f>'Income Statement'!D18/Assumptions!$C$96</f>
+        <f>'Income Statement'!D18/Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="E7" s="39">
-        <f>'Income Statement'!E18/Assumptions!$C$96</f>
+        <f>'Income Statement'!E18/Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="F7" s="39">
-        <f>'Income Statement'!F18/Assumptions!$C$96</f>
+        <f>'Income Statement'!F18/Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="G7" s="39">
-        <f>'Income Statement'!G18/Assumptions!$C$96</f>
+        <f>'Income Statement'!G18/Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="H7" s="39">
-        <f>'Income Statement'!H18/Assumptions!$C$96</f>
+        <f>'Income Statement'!H18/Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="I7" s="39">
-        <f>'Income Statement'!I18/Assumptions!$C$96</f>
+        <f>'Income Statement'!I18/Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -6118,27 +6118,27 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <f>Assumptions!$C$96/'Income Statement'!D18</f>
+        <f>Assumptions!$C$97/'Income Statement'!D18</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>Assumptions!$C$96/'Income Statement'!E18</f>
+        <f>Assumptions!$C$97/'Income Statement'!E18</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>Assumptions!$C$96/'Income Statement'!F18</f>
+        <f>Assumptions!$C$97/'Income Statement'!F18</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>Assumptions!$C$96/'Income Statement'!G18</f>
+        <f>Assumptions!$C$97/'Income Statement'!G18</f>
         <v/>
       </c>
       <c r="H17" s="10">
-        <f>Assumptions!$C$96/'Income Statement'!H18</f>
+        <f>Assumptions!$C$97/'Income Statement'!H18</f>
         <v/>
       </c>
       <c r="I17" s="10">
-        <f>Assumptions!$C$96/'Income Statement'!I18</f>
+        <f>Assumptions!$C$97/'Income Statement'!I18</f>
         <v/>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="B10" s="38">
-        <f>Assumptions!$C$99</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="C10" s="38">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="B11" s="38">
-        <f>Assumptions!$C$100</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
       <c r="C11" s="38">
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="B12" s="38">
-        <f>Assumptions!$C$101</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="C12" s="38">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>Assumptions!$C$96/Assumptions!$C$6/Assumptions!$C$5</f>
+        <f>Assumptions!$C$97/Assumptions!$C$6/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
         <v/>
       </c>
       <c r="C5" s="8">
-        <f>Assumptions!$C$102</f>
+        <f>Assumptions!$C$103</f>
         <v/>
       </c>
       <c r="D5" s="9">
@@ -6487,7 +6487,7 @@
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>Assumptions!$C$103</f>
+        <f>Assumptions!$C$104</f>
         <v/>
       </c>
       <c r="D6" s="9">
@@ -6510,7 +6510,7 @@
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>Assumptions!$C$104</f>
+        <f>Assumptions!$C$105</f>
         <v/>
       </c>
       <c r="D7" s="9">
@@ -6533,7 +6533,7 @@
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>Assumptions!$C$105</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
       <c r="D8" s="9">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>Assumptions!$C$102*Sensitivity!C50+Assumptions!$C$103*B6+Assumptions!$C$104*B7+Assumptions!$C$105*B8</f>
+        <f>Assumptions!$C$103*Sensitivity!C50+Assumptions!$C$104*B6+Assumptions!$C$105*B7+Assumptions!$C$106*B8</f>
         <v/>
       </c>
       <c r="E10" s="10">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>Assumptions!$C$102*'SOTP Bridge'!D14+Assumptions!$C$103*B6+Assumptions!$C$104*'Relative &amp; Normalized'!C34+Assumptions!$C$105*'Relative &amp; Normalized'!C41</f>
+        <f>Assumptions!$C$103*'SOTP Bridge'!D14+Assumptions!$C$104*B6+Assumptions!$C$105*'Relative &amp; Normalized'!C34+Assumptions!$C$106*'Relative &amp; Normalized'!C41</f>
         <v/>
       </c>
       <c r="E11" s="10">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>Assumptions!$C$102*Sensitivity!C72+Assumptions!$C$103*B6+Assumptions!$C$104*'Relative &amp; Normalized'!C34+Assumptions!$C$105*'Relative &amp; Normalized'!C41</f>
+        <f>Assumptions!$C$103*Sensitivity!C72+Assumptions!$C$104*B6+Assumptions!$C$105*'Relative &amp; Normalized'!C34+Assumptions!$C$106*'Relative &amp; Normalized'!C41</f>
         <v/>
       </c>
       <c r="E12" s="10">
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>Assumptions!$C$106</f>
+        <f>Assumptions!$C$107</f>
         <v/>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="B34" s="8">
-        <f>Assumptions!$C$80</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="B35" s="8">
-        <f>Assumptions!$C$81</f>
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="C24" s="7">
-        <f>Assumptions!$C$106</f>
+        <f>Assumptions!$C$107</f>
         <v/>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -8285,367 +8285,372 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Weighted asset life, DERIVED from notes 5, 6 and 7 (years)</t>
+          <t>Average age of the base, MEASURED from notes 5, 6 and 7 (years)</t>
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>28.09842122488282</v>
+        <v>10.28935645372001</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Audited consolidated financial statements for the year ended 31 December 2025, signed 9 February 2026, obtained from the company's own investor-relations page, notes 5, 6 and 7, DERIVED BY IDENTITY from those notes' own cost and charge columns and LABELLED as derived, and READ BY OCR OFF THE RENDERED PIXELS because the filing carries no usable text layer (85 bytes across 85 pages) and its property note is printed landscape, so the page was rotated before it could be read. ARITHMETIC IS THE ARBITER AND THE EXTRACTION FOOTS FOUR WAYS: the cost columns sum to the printed total of 10,929,327; the accumulated-depreciation columns to 3,734,337; cost less accumulated reproduces the balance sheet's 7,194,990; and the year's charge of 352,199 splits to the 341,696 in cost of sales and 10,503 in general and administrative expenses the notes state separately. Property, plant and equipment 10,001,105 (total less land, which is never depreciated, and less capital work in progress, whose accumulated column is impairment rather than depreciation) over 352,199 gives 28.40 years; right-of-use 22,649 over 5,361 gives 4.22; intangibles are DISCLOSED at 30 years outright and their gross cost follows from the flat charge. Blended, 28.10 years, cross-checked at 27.88 on FY2024's own columns. The right-of-use figure does NOT match the 15-year equipment lease the note names, and the note explains why rather than contradicting it: the book is 19,997 of buildings against 2,652 of equipment, and the buildings are a head office and labour accommodation on ONE-YEAR terms (2026-02-09)</t>
+          <t>Audited consolidated financial statements for the year ended 31 December 2025, signed 9 February 2026, obtained from the company's own investor-relations page, notes 5, 6 and 7. THE AVERAGE AGE OF THE BASE, MEASURED rather than assumed: accumulated depreciation over the year's own charge is, under the straight-line method these accounts use, exactly the charge-weighted average age of the assets bearing that charge — an identity, not an estimate. The property note prints its accumulated column (3,734,337); neither the right-of-use nor the intangible note does, so both are recovered by the identity gross less net (22,649 less 1,878; 364,710 less 315,668) and LABELLED as derived. The three sum to 3,804,150 over a charge of 369,717 = 10.29 years. THIS BASE IS YOUNGER THAN UNIFORM — half the 28.10-year life would put it at 14.05 — so escalating the book charge over half the life OVERSTATES what replacement costs, by 7.2% at this market's 2% terminal. The distinction matters because the escalation is over the AGE of the assets, and half the life is that age only where vintages are uniform, which here they are not (2026-09-04)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Invested capital per unit of real growth (AED mn)</t>
+          <t>Weighted asset life, DERIVED from notes 5, 6 and 7 (years)</t>
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>5526.341086457007</v>
+        <v>28.09842122488282</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>One per cent of real growth costs one per cent of the invested capital the business operates on. The marginal reading across the explicit window is NEGATIVE here, because the plant is written down faster than capex replaces it over those five years, and a negative capital requirement would credit this company for growing</t>
+          <t>Audited consolidated financial statements for the year ended 31 December 2025, signed 9 February 2026, obtained from the company's own investor-relations page, notes 5, 6 and 7, DERIVED BY IDENTITY from those notes' own cost and charge columns and LABELLED as derived, and READ BY OCR OFF THE RENDERED PIXELS because the filing carries no usable text layer (85 bytes across 85 pages) and its property note is printed landscape, so the page was rotated before it could be read. ARITHMETIC IS THE ARBITER AND THE EXTRACTION FOOTS FOUR WAYS: the cost columns sum to the printed total of 10,929,327; the accumulated-depreciation columns to 3,734,337; cost less accumulated reproduces the balance sheet's 7,194,990; and the year's charge of 352,199 splits to the 341,696 in cost of sales and 10,503 in general and administrative expenses the notes state separately. Property, plant and equipment 10,001,105 (total less land, which is never depreciated, and less capital work in progress, whose accumulated column is impairment rather than depreciation) over 352,199 gives 28.40 years; right-of-use 22,649 over 5,361 gives 4.22; intangibles are DISCLOSED at 30 years outright and their gross cost follows from the flat charge. Blended, 28.10 years, cross-checked at 27.88 on FY2024's own columns. The right-of-use figure does NOT match the 15-year equipment lease the note names, and the note explains why rather than contradicting it: the book is 19,997 of buildings against 2,652 of equipment, and the buildings are a head office and labour accommodation on ONE-YEAR terms (2026-02-09)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Growth, FY2031-FY2040 window — (1+inflation)(1+real)-1</t>
-        </is>
-      </c>
-      <c r="C80" s="10">
-        <f>(1+$C$75)*(1+$C$76)-1</f>
-        <v/>
+          <t>Invested capital per unit of real growth (AED mn)</t>
+        </is>
+      </c>
+      <c r="C80" s="25" t="n">
+        <v>5526.341086457007</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>DERIVED from the two rows above, never typed. It reproduces the previous edition's 2.50% to the basis point, because under a tariff the regulator does not index a nominal growth rate IS a volume assumption</t>
+          <t>One per cent of real growth costs one per cent of the invested capital the business operates on. The marginal reading across the explicit window is NEGATIVE here, because the plant is written down faster than capex replaces it over those five years, and a negative capital requirement would credit this company for growing</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Growth beyond FY2040 — the same identity on the stage-two real rate</t>
+          <t>Growth, FY2031-FY2040 window — (1+inflation)(1+real)-1</t>
         </is>
       </c>
       <c r="C81" s="10">
-        <f>(1+$C$75)*(1+$C$77)-1</f>
+        <f>(1+$C$75)*(1+$C$76)-1</f>
         <v/>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>DERIVED. Reproduces the previous edition's 1.50%, and makes visible that it is a real DECLINE of half a point a year</t>
+          <t>DERIVED from the two rows above, never typed. It reproduces the previous edition's 2.50% to the basis point, because under a tariff the regulator does not index a nominal growth rate IS a volume assumption</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
+          <t>Growth beyond FY2040 — the same identity on the stage-two real rate</t>
+        </is>
+      </c>
+      <c r="C82" s="10">
+        <f>(1+$C$75)*(1+$C$77)-1</f>
+        <v/>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>DERIVED. Reproduces the previous edition's 1.50%, and makes visible that it is a real DECLINE of half a point a year</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
           <t>Stub period — 30-Jun-2026 anchor to end-FY2026 (years)</t>
         </is>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.4999999999999997</v>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t>The bridge is struck on the 30-Jun-2026 reviewed balance sheet, so the cash-flow clock starts there too: FY2026 contributes its second half only and later year-ends sit at 1.5 to 4.5 years</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="11" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>Bridge — 30-Jun-2026 reviewed balance sheet</t>
         </is>
       </c>
-      <c r="B84" s="14" t="n"/>
-      <c r="C84" s="14" t="n"/>
-      <c r="D84" s="14" t="n"/>
-      <c r="E84" s="14" t="n"/>
-      <c r="F84" s="14" t="n"/>
-      <c r="G84" s="14" t="n"/>
-      <c r="H84" s="14" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>Bank borrowings (AED mn)</t>
-        </is>
-      </c>
-      <c r="C85" s="25" t="n">
-        <v>5502.845</v>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>Bank borrowings 30-Jun-2026: current 2.845 + non-current 5,500.000, reviewed interim BS (2026-08-05)</t>
-        </is>
-      </c>
+      <c r="B85" s="14" t="n"/>
+      <c r="C85" s="14" t="n"/>
+      <c r="D85" s="14" t="n"/>
+      <c r="E85" s="14" t="n"/>
+      <c r="F85" s="14" t="n"/>
+      <c r="G85" s="14" t="n"/>
+      <c r="H85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities (AED mn)</t>
+          <t>Bank borrowings (AED mn)</t>
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>0.872</v>
+        <v>5502.845</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Lease liabilities 30-Jun-2026 (2026-08-05)</t>
+          <t>Bank borrowings 30-Jun-2026: current 2.845 + non-current 5,500.000, reviewed interim BS (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents (AED mn)</t>
+          <t>Lease liabilities (AED mn)</t>
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>2472.012</v>
+        <v>0.872</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents 30-Jun-2026 (2026-08-05)</t>
+          <t>Lease liabilities 30-Jun-2026 (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Term deposits (AED mn)</t>
+          <t>Cash and cash equivalents (AED mn)</t>
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>40.212</v>
+        <v>2472.012</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Term deposits (&gt;3m) 30-Jun-2026 (2026-08-05)</t>
+          <t>Cash and cash equivalents 30-Jun-2026 (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Related-party acquisition receivables at book (Note 8: 1,005.0 Dubai Aviation City + 289.4 Nakheel) (AED mn)</t>
+          <t>Term deposits (AED mn)</t>
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>1294.442</v>
+        <v>40.212</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Financial assets at amortised cost, 30-Jun-2026 reviewed BS: non-current 1,273.130 + current 21.312. Note 8 composition: AED 1,005.030 from Dubai Aviation City Corporation (DXB CoolCo acquisition, 2023) + AED 289.412 from Nakheel PJSC (Empower Snow acquisition, 2021) — related-party acquisition receivables under common control, NOT an operating concession asset. Clean financial-asset treatment adopted per critique (17-Aug-2026): interest income excluded from operating EBITDA/FCFF, asset added at book in the EV-to-equity bridge, and excluded from terminal invested capital (2026-08-05)</t>
+          <t>Term deposits (&gt;3m) 30-Jun-2026 (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Investment properties (AED mn)</t>
+          <t>Related-party acquisition receivables at book (Note 8: 1,005.0 Dubai Aviation City + 289.4 Nakheel) (AED mn)</t>
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>168.716</v>
+        <v>1294.442</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Investment properties 30-Jun-2026 (non-operating side pocket, added in the bridge at book) (2026-08-05)</t>
+          <t>Financial assets at amortised cost, 30-Jun-2026 reviewed BS: non-current 1,273.130 + current 21.312. Note 8 composition: AED 1,005.030 from Dubai Aviation City Corporation (DXB CoolCo acquisition, 2023) + AED 289.412 from Nakheel PJSC (Empower Snow acquisition, 2021) — related-party acquisition receivables under common control, NOT an operating concession asset. Clean financial-asset treatment adopted per critique (17-Aug-2026): interest income excluded from operating EBITDA/FCFF, asset added at book in the EV-to-equity bridge, and excluded from terminal invested capital (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at fair value through profit or loss (AED mn)</t>
+          <t>Investment properties (AED mn)</t>
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>53.411</v>
+        <v>168.716</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Financial assets at FVTPL 30-Jun-2026 (cash-like, added in the bridge) (2026-08-05)</t>
+          <t>Investment properties 30-Jun-2026 (non-operating side pocket, added in the bridge at book) (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at fair value through OCI (AED mn)</t>
+          <t>Financial assets at fair value through profit or loss (AED mn)</t>
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>74.56399999999999</v>
+        <v>53.411</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Financial assets at FVOCI 30-Jun-2026 (added at book) (2026-08-05)</t>
+          <t>Financial assets at FVTPL 30-Jun-2026 (cash-like, added in the bridge) (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to shareholders, 30-Jun-2026 (AED mn)</t>
+          <t>Financial assets at fair value through OCI (AED mn)</t>
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>3337.585</v>
+        <v>74.56399999999999</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Equity attributable to holders, 30-Jun-2026 reviewed BS (2026-08-05)</t>
+          <t>Financial assets at FVOCI 30-Jun-2026 (added at book) (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests, 30-Jun-2026 (AED mn)</t>
+          <t>Equity attributable to shareholders, 30-Jun-2026 (AED mn)</t>
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>190.745</v>
+        <v>3337.585</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests (15% of DXB CoolCo et al. — the H1-2026 subsidiary note shows Dxb CoolCo FZCO at 85%/85%), 30-Jun-2026 reviewed BS (2026-08-05)</t>
+          <t>Equity attributable to holders, 30-Jun-2026 reviewed BS (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Yield earned on cash balances</t>
-        </is>
-      </c>
-      <c r="C95" s="30" t="n">
-        <v>0.03500000000000009</v>
+          <t>Non-controlling interests, 30-Jun-2026 (AED mn)</t>
+        </is>
+      </c>
+      <c r="C95" s="25" t="n">
+        <v>190.745</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Deposit-rate assumption used in the forecast finance line; flagged as an estimate</t>
+          <t>Non-controlling interests (15% of DXB CoolCo et al. — the H1-2026 subsidiary note shows Dxb CoolCo FZCO at 85%/85%), 30-Jun-2026 reviewed BS (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
+          <t>Yield earned on cash balances</t>
+        </is>
+      </c>
+      <c r="C96" s="30" t="n">
+        <v>0.03500000000000009</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Deposit-rate assumption used in the forecast finance line; flagged as an estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
           <t>Committed annual dividend (AED mn)</t>
         </is>
       </c>
-      <c r="C96" s="25" t="n">
+      <c r="C97" s="25" t="n">
         <v>875</v>
       </c>
-      <c r="H96" s="4" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>Dividend AED 875m/yr committed for 2025 AND 2026 (2 x 437.5m, Oct/Apr), deck p12; FY2025 FS note 39: 875.0 paid in 2025 (2026-08-05)</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="11" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>Valuation lenses</t>
         </is>
       </c>
-      <c r="B98" s="14" t="n"/>
-      <c r="C98" s="14" t="n"/>
-      <c r="D98" s="14" t="n"/>
-      <c r="E98" s="14" t="n"/>
-      <c r="F98" s="14" t="n"/>
-      <c r="G98" s="14" t="n"/>
-      <c r="H98" s="14" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Peer EV/EBITDA — Tabreed (trailing, restruck at the anchor)</t>
-        </is>
-      </c>
-      <c r="C99" s="32" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>Tabreed (DFM) FY2025 results at the 2026-08-07 anchor (restruck: Tabreed 2.46 on 6/7-Aug; 0.5x of multiple = AED 0.078/share on this lens)</t>
-        </is>
-      </c>
+      <c r="B99" s="14" t="n"/>
+      <c r="C99" s="14" t="n"/>
+      <c r="D99" s="14" t="n"/>
+      <c r="E99" s="14" t="n"/>
+      <c r="F99" s="14" t="n"/>
+      <c r="G99" s="14" t="n"/>
+      <c r="H99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Peer price/earnings — Tabreed (trailing, restruck at the anchor)</t>
+          <t>Peer EV/EBITDA — Tabreed (trailing, restruck at the anchor)</t>
         </is>
       </c>
       <c r="C100" s="32" t="n">
-        <v>15</v>
+        <v>10.1</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Tabreed (DFM), close 2.46 on 6/7-Aug-2026 — cross-check input only</t>
+          <t>Tabreed (DFM) FY2025 results at the 2026-08-07 anchor (restruck: Tabreed 2.46 on 6/7-Aug; 0.5x of multiple = AED 0.078/share on this lens)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>Peer price/earnings — DEWA (parent)</t>
+          <t>Peer price/earnings — Tabreed (trailing, restruck at the anchor)</t>
         </is>
       </c>
       <c r="C101" s="32" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>DEWA (DFM), Aug-2026 — context only, majority owner</t>
+          <t>Tabreed (DFM), close 2.46 on 6/7-Aug-2026 — cross-check input only</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C102" s="24" t="n">
-        <v>0.5</v>
+          <t>Peer price/earnings — DEWA (parent)</t>
+        </is>
+      </c>
+      <c r="C102" s="32" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>DEWA (DFM), Aug-2026 — context only, majority owner</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative multiples</t>
+          <t>Weight — discounted cash flow</t>
         </is>
       </c>
       <c r="C103" s="24" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised earnings</t>
+          <t>Weight — relative multiples</t>
         </is>
       </c>
       <c r="C104" s="24" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Weight — book value</t>
+          <t>Weight — normalised earnings</t>
         </is>
       </c>
       <c r="C105" s="24" t="n">
@@ -8655,13 +8660,23 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
+          <t>Weight — book value</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
           <t>DEWA control-transaction price, Feb-2026 (AED)</t>
         </is>
       </c>
-      <c r="C106" s="22" t="n">
+      <c r="C107" s="22" t="n">
         <v>2.16</v>
       </c>
-      <c r="H106" s="4" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr">
         <is>
           <t>Related-party CONTROL price for Dubai Holding's 24% stake — a disclosed reference point, never fair value</t>
         </is>
@@ -8776,15 +8791,15 @@
         </is>
       </c>
       <c r="C7" s="19">
-        <f>Assumptions!$C$89</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="D7" s="19">
-        <f>Assumptions!$C$89</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="E7" s="19">
-        <f>Assumptions!$C$89</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -8795,15 +8810,15 @@
         </is>
       </c>
       <c r="C8" s="19">
-        <f>Assumptions!$C$90</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
       <c r="D8" s="19">
-        <f>Assumptions!$C$90</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
       <c r="E8" s="19">
-        <f>Assumptions!$C$90</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
     </row>
@@ -8814,15 +8829,15 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="D9" s="19">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="E9" s="19">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -8833,15 +8848,15 @@
         </is>
       </c>
       <c r="C10" s="19">
-        <f>Assumptions!$C$92</f>
+        <f>Assumptions!$C$93</f>
         <v/>
       </c>
       <c r="D10" s="19">
-        <f>Assumptions!$C$92</f>
+        <f>Assumptions!$C$93</f>
         <v/>
       </c>
       <c r="E10" s="19">
-        <f>Assumptions!$C$92</f>
+        <f>Assumptions!$C$93</f>
         <v/>
       </c>
     </row>
@@ -9765,7 +9780,7 @@
         </is>
       </c>
       <c r="C6" s="38">
-        <f>Assumptions!$C$99</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
     </row>
@@ -9798,7 +9813,7 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$C$89</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -9809,7 +9824,7 @@
         </is>
       </c>
       <c r="C10" s="19">
-        <f>Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92</f>
+        <f>Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93</f>
         <v/>
       </c>
     </row>
@@ -9854,7 +9869,7 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>Assumptions!$C$100*'Income Statement'!E18/Assumptions!$C$6</f>
+        <f>Assumptions!$C$101*'Income Statement'!E18/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -10012,7 +10027,7 @@
         </is>
       </c>
       <c r="C30" s="38">
-        <f>(1-Assumptions!$C$80/C29)/(DCF!$C$50-Assumptions!$C$80)</f>
+        <f>(1-Assumptions!$C$81/C29)/(DCF!$C$50-Assumptions!$C$81)</f>
         <v/>
       </c>
     </row>
@@ -10046,7 +10061,7 @@
         </is>
       </c>
       <c r="C33" s="38">
-        <f>(1-Assumptions!$C$80/C32)/(DCF!$C$50-Assumptions!$C$80)</f>
+        <f>(1-Assumptions!$C$81/C32)/(DCF!$C$50-Assumptions!$C$81)</f>
         <v/>
       </c>
     </row>
@@ -10081,7 +10096,7 @@
         </is>
       </c>
       <c r="C37" s="9">
-        <f>Assumptions!$C$93/Assumptions!$C$6</f>
+        <f>Assumptions!$C$94/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -10092,7 +10107,7 @@
         </is>
       </c>
       <c r="C38" s="38">
-        <f>(C29-Assumptions!$C$80)/(DCF!$C$50-Assumptions!$C$80)</f>
+        <f>(C29-Assumptions!$C$81)/(DCF!$C$50-Assumptions!$C$81)</f>
         <v/>
       </c>
     </row>
@@ -10115,7 +10130,7 @@
         </is>
       </c>
       <c r="C40" s="38">
-        <f>(C32-Assumptions!$C$80)/(DCF!$C$50-Assumptions!$C$80)</f>
+        <f>(C32-Assumptions!$C$81)/(DCF!$C$50-Assumptions!$C$81)</f>
         <v/>
       </c>
     </row>
@@ -10150,7 +10165,7 @@
         </is>
       </c>
       <c r="C44" s="9">
-        <f>Assumptions!$C$96/Assumptions!$C$6</f>
+        <f>Assumptions!$C$97/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -10161,7 +10176,7 @@
         </is>
       </c>
       <c r="C45" s="7">
-        <f>C44*(1+Assumptions!$C$80)/(DCF!$C$50-Assumptions!$C$80)</f>
+        <f>C44*(1+Assumptions!$C$81)/(DCF!$C$50-Assumptions!$C$81)</f>
         <v/>
       </c>
     </row>
@@ -10635,7 +10650,7 @@
         </is>
       </c>
       <c r="B19" s="41">
-        <f>Assumptions!$C$82</f>
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="C19" s="42">
@@ -10689,7 +10704,7 @@
         </is>
       </c>
       <c r="B21" s="43">
-        <f>B18*B20*Assumptions!$C$82</f>
+        <f>B18*B20*Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="C21" s="43">
@@ -10763,7 +10778,7 @@
         </is>
       </c>
       <c r="C27" s="8">
-        <f>Assumptions!$C$80</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -10785,7 +10800,7 @@
         </is>
       </c>
       <c r="C29" s="8">
-        <f>Assumptions!$C$81</f>
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
     </row>
@@ -11056,7 +11071,7 @@
         </is>
       </c>
       <c r="C53" s="19">
-        <f>Assumptions!$C$85+Assumptions!$C$86-Assumptions!$C$87-Assumptions!$C$88</f>
+        <f>Assumptions!$C$86+Assumptions!$C$87-Assumptions!$C$88-Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -11191,7 +11206,7 @@
         </is>
       </c>
       <c r="B64" s="28">
-        <f>B63*B20*Assumptions!$C$82</f>
+        <f>B63*B20*Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="C64" s="28">
@@ -11346,7 +11361,7 @@
         </is>
       </c>
       <c r="B78" s="28">
-        <f>B18/(1+$D$56)^B19*Assumptions!$C$82</f>
+        <f>B18/(1+$D$56)^B19*Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="C78" s="28">
@@ -11395,7 +11410,7 @@
         </is>
       </c>
       <c r="C81" s="28">
-        <f>1408.881541</f>
+        <f>1448.550594</f>
         <v/>
       </c>
     </row>
@@ -11417,7 +11432,7 @@
         </is>
       </c>
       <c r="C83" s="28">
-        <f>1820.231542*(1+C29)/(($D$56-C29)*(1+$D$56)^10)</f>
+        <f>1870.515870*(1+C29)/(($D$56-C29)*(1+$D$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -11521,7 +11536,7 @@
         </is>
       </c>
       <c r="B91" s="27">
-        <f>(C52*C50+(Assumptions!$C$85+Assumptions!$C$86)*C51*(1-Assumptions!$C$7))/(C52+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>(C52*C50+(Assumptions!$C$86+Assumptions!$C$87)*C51*(1-Assumptions!$C$7))/(C52+Assumptions!$C$86+Assumptions!$C$87)</f>
         <v/>
       </c>
       <c r="C91" s="7">
@@ -11541,7 +11556,7 @@
         </is>
       </c>
       <c r="B92" s="27">
-        <f>C55*C50+C54*(((Assumptions!$C$85+Assumptions!$C$86)*C51*(1-Assumptions!$C$7)-(Assumptions!$C$87+Assumptions!$C$88)*Assumptions!$C$95*(1-Assumptions!$C$7))/C53)</f>
+        <f>C55*C50+C54*(((Assumptions!$C$86+Assumptions!$C$87)*C51*(1-Assumptions!$C$7)-(Assumptions!$C$88+Assumptions!$C$89)*Assumptions!$C$96*(1-Assumptions!$C$7))/C53)</f>
         <v/>
       </c>
       <c r="C92" s="7">
@@ -11607,15 +11622,15 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Stage one, FY2031 — less capital maintenance at replacement cost, that charge escalated over half the derived life</t>
+          <t>Stage one, FY2031 — less capital maintenance at replacement cost, that charge escalated over the MEASURED age of the base</t>
         </is>
       </c>
       <c r="C96" s="28">
-        <f>-C95*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
+        <f>-C95*(1+Assumptions!$C$75)^Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="G96" s="28">
-        <f>-G95*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
+        <f>-G95*(1+Assumptions!$C$75)^Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
@@ -11697,15 +11712,15 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Stage two, FY2041 — less capital maintenance at replacement cost, that charge escalated over half the derived life</t>
+          <t>Stage two, FY2041 — less capital maintenance at replacement cost, that charge escalated over the MEASURED age of the base</t>
         </is>
       </c>
       <c r="C105" s="28">
-        <f>-C104*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
+        <f>-C104*(1+Assumptions!$C$75)^Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="G105" s="28">
-        <f>-G104*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
+        <f>-G104*(1+Assumptions!$C$75)^Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
@@ -12185,23 +12200,23 @@
         <v/>
       </c>
       <c r="E13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*Assumptions!$C$87)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*Assumptions!$C$88)</f>
         <v/>
       </c>
       <c r="F13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!E9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*'Balance Sheet'!E9)</f>
         <v/>
       </c>
       <c r="G13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!F9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*'Balance Sheet'!F9)</f>
         <v/>
       </c>
       <c r="H13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!G9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*'Balance Sheet'!G9)</f>
         <v/>
       </c>
       <c r="I13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!H9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*'Balance Sheet'!H9)</f>
         <v/>
       </c>
     </row>

--- a/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
+++ b/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
@@ -1236,23 +1236,23 @@
         <v>2512.224</v>
       </c>
       <c r="E9" s="28">
-        <f>(Assumptions!$C$86+Assumptions!$C$87)-E16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-E16</f>
         <v/>
       </c>
       <c r="F9" s="28">
-        <f>(Assumptions!$C$86+Assumptions!$C$87)-F16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-F16</f>
         <v/>
       </c>
       <c r="G9" s="28">
-        <f>(Assumptions!$C$86+Assumptions!$C$87)-G16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-G16</f>
         <v/>
       </c>
       <c r="H9" s="28">
-        <f>(Assumptions!$C$86+Assumptions!$C$87)-H16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-H16</f>
         <v/>
       </c>
       <c r="I9" s="28">
-        <f>(Assumptions!$C$86+Assumptions!$C$87)-I16</f>
+        <f>(Assumptions!$C$85+Assumptions!$C$86)-I16</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
         <v>5503.717</v>
       </c>
       <c r="E11" s="28">
-        <f>Assumptions!$C$86+Assumptions!$C$87</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F11" s="28">
-        <f>Assumptions!$C$86+Assumptions!$C$87</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="G11" s="28">
-        <f>Assumptions!$C$86+Assumptions!$C$87</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="H11" s="28">
-        <f>Assumptions!$C$86+Assumptions!$C$87</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="I11" s="28">
-        <f>Assumptions!$C$86+Assumptions!$C$87</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86</f>
         <v/>
       </c>
     </row>
@@ -1389,27 +1389,27 @@
         <v/>
       </c>
       <c r="D13" s="33">
-        <f>Assumptions!$C$94</f>
+        <f>Assumptions!$C$93</f>
         <v/>
       </c>
       <c r="E13" s="33">
-        <f>$D13+Assumptions!$C$83*('Income Statement'!E18-Assumptions!$C$97)</f>
+        <f>$D13+Assumptions!$C$82*('Income Statement'!E18-Assumptions!$C$96)</f>
         <v/>
       </c>
       <c r="F13" s="33">
-        <f>E13+'Income Statement'!F18-Assumptions!$C$97</f>
+        <f>E13+'Income Statement'!F18-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="G13" s="33">
-        <f>F13+'Income Statement'!G18-Assumptions!$C$97</f>
+        <f>F13+'Income Statement'!G18-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="H13" s="33">
-        <f>G13+'Income Statement'!H18-Assumptions!$C$97</f>
+        <f>G13+'Income Statement'!H18-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="I13" s="33">
-        <f>H13+'Income Statement'!I18-Assumptions!$C$97</f>
+        <f>H13+'Income Statement'!I18-Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -1426,11 +1426,11 @@
         <v>186.378</v>
       </c>
       <c r="D14" s="19">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="E14" s="28">
-        <f>$D14-Assumptions!$C$83*'Income Statement'!E17</f>
+        <f>$D14-Assumptions!$C$82*'Income Statement'!E17</f>
         <v/>
       </c>
       <c r="F14" s="28">
@@ -1510,23 +1510,23 @@
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>$D16-Assumptions!$C$83*(DCF!B18+('Income Statement'!E13+'Income Statement'!E6+'Income Statement'!E7)*(1-Assumptions!$C$7)-Assumptions!$C$97)</f>
+        <f>$D16-Assumptions!$C$82*(DCF!B18+('Income Statement'!E13+'Income Statement'!E6+'Income Statement'!E7)*(1-Assumptions!$C$7)-Assumptions!$C$96)</f>
         <v/>
       </c>
       <c r="F16" s="33">
-        <f>E16-(DCF!C18+('Income Statement'!F13+'Income Statement'!F6+'Income Statement'!F7)*(1-Assumptions!$C$7))+Assumptions!$C$97</f>
+        <f>E16-(DCF!C18+('Income Statement'!F13+'Income Statement'!F6+'Income Statement'!F7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="G16" s="33">
-        <f>F16-(DCF!D18+('Income Statement'!G13+'Income Statement'!G6+'Income Statement'!G7)*(1-Assumptions!$C$7))+Assumptions!$C$97</f>
+        <f>F16-(DCF!D18+('Income Statement'!G13+'Income Statement'!G6+'Income Statement'!G7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="H16" s="33">
-        <f>G16-(DCF!E18+('Income Statement'!H13+'Income Statement'!H6+'Income Statement'!H7)*(1-Assumptions!$C$7))+Assumptions!$C$97</f>
+        <f>G16-(DCF!E18+('Income Statement'!H13+'Income Statement'!H6+'Income Statement'!H7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="I16" s="33">
-        <f>H16-(DCF!F18+('Income Statement'!I13+'Income Statement'!I6+'Income Statement'!I7)*(1-Assumptions!$C$7))+Assumptions!$C$97</f>
+        <f>H16-(DCF!F18+('Income Statement'!I13+'Income Statement'!I6+'Income Statement'!I7)*(1-Assumptions!$C$7))+Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -2044,23 +2044,23 @@
         <v>-875</v>
       </c>
       <c r="D15" s="19">
-        <f>-Assumptions!$C$97</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="E15" s="19">
-        <f>-Assumptions!$C$97</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="F15" s="19">
-        <f>-Assumptions!$C$97</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="G15" s="19">
-        <f>-Assumptions!$C$97</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="H15" s="19">
-        <f>-Assumptions!$C$97</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -3139,23 +3139,23 @@
         </is>
       </c>
       <c r="B14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-B13/DCF!$C$26)*((1+B13)/(1+DCF!$C$56))*(1-((1+B13)/(1+DCF!$C$56))^10)/(1-((1+B13)/(1+DCF!$C$56)))+DCF!$F$14*(1+B13)^10*(1+MIN(Assumptions!$C$82,B13))*(1-MIN(Assumptions!$C$82,B13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,B13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-B13/DCF!$C$26)*((1+B13)/(1+DCF!$C$56))*(1-((1+B13)/(1+DCF!$C$56))^10)/(1-((1+B13)/(1+DCF!$C$56)))+DCF!$F$14*(1+B13)^10*(1+MIN(Assumptions!$C$81,B13))*(1-MIN(Assumptions!$C$81,B13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,B13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-C13/DCF!$C$26)*((1+C13)/(1+DCF!$C$56))*(1-((1+C13)/(1+DCF!$C$56))^10)/(1-((1+C13)/(1+DCF!$C$56)))+DCF!$F$14*(1+C13)^10*(1+MIN(Assumptions!$C$82,C13))*(1-MIN(Assumptions!$C$82,C13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,C13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-C13/DCF!$C$26)*((1+C13)/(1+DCF!$C$56))*(1-((1+C13)/(1+DCF!$C$56))^10)/(1-((1+C13)/(1+DCF!$C$56)))+DCF!$F$14*(1+C13)^10*(1+MIN(Assumptions!$C$81,C13))*(1-MIN(Assumptions!$C$81,C13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,C13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-D13/DCF!$C$26)*((1+D13)/(1+DCF!$C$56))*(1-((1+D13)/(1+DCF!$C$56))^10)/(1-((1+D13)/(1+DCF!$C$56)))+DCF!$F$14*(1+D13)^10*(1+MIN(Assumptions!$C$82,D13))*(1-MIN(Assumptions!$C$82,D13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,D13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-D13/DCF!$C$26)*((1+D13)/(1+DCF!$C$56))*(1-((1+D13)/(1+DCF!$C$56))^10)/(1-((1+D13)/(1+DCF!$C$56)))+DCF!$F$14*(1+D13)^10*(1+MIN(Assumptions!$C$81,D13))*(1-MIN(Assumptions!$C$81,D13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,D13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-E13/DCF!$C$26)*((1+E13)/(1+DCF!$C$56))*(1-((1+E13)/(1+DCF!$C$56))^10)/(1-((1+E13)/(1+DCF!$C$56)))+DCF!$F$14*(1+E13)^10*(1+MIN(Assumptions!$C$82,E13))*(1-MIN(Assumptions!$C$82,E13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,E13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-E13/DCF!$C$26)*((1+E13)/(1+DCF!$C$56))*(1-((1+E13)/(1+DCF!$C$56))^10)/(1-((1+E13)/(1+DCF!$C$56)))+DCF!$F$14*(1+E13)^10*(1+MIN(Assumptions!$C$81,E13))*(1-MIN(Assumptions!$C$81,E13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,E13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>((DCF!$C$37+(DCF!$F$14*(1-F13/DCF!$C$26)*((1+F13)/(1+DCF!$C$56))*(1-((1+F13)/(1+DCF!$C$56))^10)/(1-((1+F13)/(1+DCF!$C$56)))+DCF!$F$14*(1+F13)^10*(1+MIN(Assumptions!$C$82,F13))*(1-MIN(Assumptions!$C$82,F13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$82,F13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>((DCF!$C$37+(DCF!$F$14*(1-F13/DCF!$C$26)*((1+F13)/(1+DCF!$C$56))*(1-((1+F13)/(1+DCF!$C$56))^10)/(1-((1+F13)/(1+DCF!$C$56)))+DCF!$F$14*(1+F13)^10*(1+MIN(Assumptions!$C$81,F13))*(1-MIN(Assumptions!$C$81,F13)/DCF!$C$26)/((DCF!$C$56-MIN(Assumptions!$C$81,F13))*(1+DCF!$C$56)^10))*DCF!$F$20)-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -3616,23 +3616,23 @@
         </is>
       </c>
       <c r="B35" s="28">
-        <f>B30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>B30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>C30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>C30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="D35" s="28">
-        <f>D30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>D30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="E35" s="28">
-        <f>E30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>E30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="F35" s="28">
-        <f>F30*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>F30*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
     </row>
@@ -3805,23 +3805,23 @@
         </is>
       </c>
       <c r="B42" s="28">
-        <f>1390.755402</f>
+        <f>1351.086349</f>
         <v/>
       </c>
       <c r="C42" s="28">
-        <f>1413.873478</f>
+        <f>1374.204426</f>
         <v/>
       </c>
       <c r="D42" s="28">
-        <f>1431.212036</f>
+        <f>1391.542984</f>
         <v/>
       </c>
       <c r="E42" s="28">
-        <f>1448.550594</f>
+        <f>1408.881541</f>
         <v/>
       </c>
       <c r="F42" s="28">
-        <f>1465.889151</f>
+        <f>1426.220099</f>
         <v/>
       </c>
     </row>
@@ -3832,23 +3832,23 @@
         </is>
       </c>
       <c r="B43" s="26">
-        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="C43" s="26">
-        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="D43" s="26">
-        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="E43" s="26">
-        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
       <c r="F43" s="26">
-        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
     </row>
@@ -3886,23 +3886,23 @@
         </is>
       </c>
       <c r="B45" s="28">
-        <f>1798.042581</f>
+        <f>1747.758253</f>
         <v/>
       </c>
       <c r="C45" s="28">
-        <f>1827.031897</f>
+        <f>1776.747568</f>
         <v/>
       </c>
       <c r="D45" s="28">
-        <f>1848.773883</f>
+        <f>1798.489555</f>
         <v/>
       </c>
       <c r="E45" s="28">
-        <f>1870.515870</f>
+        <f>1820.231542</f>
         <v/>
       </c>
       <c r="F45" s="28">
-        <f>1892.257857</f>
+        <f>1841.973528</f>
         <v/>
       </c>
     </row>
@@ -3913,23 +3913,23 @@
         </is>
       </c>
       <c r="B46" s="28">
-        <f>B45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
+        <f>B45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="C46" s="28">
-        <f>C45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
+        <f>C45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="D46" s="28">
-        <f>D45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
+        <f>D45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="E46" s="28">
-        <f>E45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
+        <f>E45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
       <c r="F46" s="28">
-        <f>F45*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
+        <f>F45*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -4021,23 +4021,23 @@
         </is>
       </c>
       <c r="B50" s="34">
-        <f>(B49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(B49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>(C49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>(D49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(D49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E50" s="34">
-        <f>(E49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(E49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F50" s="34">
-        <f>(F49-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(F49-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="C58" s="28">
-        <f>C53*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>C53*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="C65" s="28">
-        <f>1315.541705</f>
+        <f>1275.872653</f>
         <v/>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="C67" s="28">
-        <f>1702.386943</f>
+        <f>1652.102614</f>
         <v/>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="C68" s="28">
-        <f>C67*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
+        <f>C67*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="C72" s="16">
-        <f>(C71-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C71-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="B89" s="28">
-        <f>B88*Assumptions!$C$83/(1+$C$91)^DCF!$B$19</f>
+        <f>B88*Assumptions!$C$82/(1+$C$91)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C89" s="28">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="C94" s="28">
-        <f>1121.543485</f>
+        <f>1086.112904</f>
         <v/>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C95" s="26">
-        <f>(1+Assumptions!$C$81)/(1+$C$91)</f>
+        <f>(1+Assumptions!$C$80)/(1+$C$91)</f>
         <v/>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C97" s="28">
-        <f>1452.006293</f>
+        <f>1407.094633</f>
         <v/>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         </is>
       </c>
       <c r="C98" s="28">
-        <f>C97*(1+Assumptions!$C$82)/(($C$91-Assumptions!$C$82)*(1+$C$91)^10)</f>
+        <f>C97*(1+Assumptions!$C$81)/(($C$91-Assumptions!$C$81)*(1+$C$91)^10)</f>
         <v/>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B102" s="14" t="n"/>
       <c r="C102" s="34">
-        <f>(C101-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C101-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D102" s="14" t="n"/>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="B116" s="28">
-        <f>B115*Assumptions!$C$83/(1+DCF!$C$56)^DCF!$B$19</f>
+        <f>B115*Assumptions!$C$82/(1+DCF!$C$56)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C116" s="28">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="C119" s="28">
-        <f>1483.954471</f>
+        <f>1443.493007</f>
         <v/>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="C120" s="26">
-        <f>(1+Assumptions!$C$81)/(1+DCF!$C$56)</f>
+        <f>(1+Assumptions!$C$80)/(1+DCF!$C$56)</f>
         <v/>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="C122" s="28">
-        <f>1916.391964</f>
+        <f>1865.103177</f>
         <v/>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="C123" s="28">
-        <f>C122*(1+Assumptions!$C$82)/((DCF!$C$56-Assumptions!$C$82)*(1+DCF!$C$56)^10)</f>
+        <f>C122*(1+Assumptions!$C$81)/((DCF!$C$56-Assumptions!$C$81)*(1+DCF!$C$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B127" s="14" t="n"/>
       <c r="C127" s="34">
-        <f>(C126-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C126-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D127" s="14" t="n"/>
@@ -5274,15 +5274,15 @@
         </is>
       </c>
       <c r="B132" s="28">
-        <f>DCF!$B$18*Assumptions!$C$83/(1+B$131)^DCF!$B$19</f>
+        <f>DCF!$B$18*Assumptions!$C$82/(1+B$131)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="C132" s="28">
-        <f>DCF!$B$18*Assumptions!$C$83/(1+C$131)^DCF!$B$19</f>
+        <f>DCF!$B$18*Assumptions!$C$82/(1+C$131)^DCF!$B$19</f>
         <v/>
       </c>
       <c r="D132" s="28">
-        <f>DCF!$B$18*Assumptions!$C$83/(1+D$131)^DCF!$B$19</f>
+        <f>DCF!$B$18*Assumptions!$C$82/(1+D$131)^DCF!$B$19</f>
         <v/>
       </c>
     </row>
@@ -5388,15 +5388,15 @@
         </is>
       </c>
       <c r="B138" s="26">
-        <f>(1+Assumptions!$C$81)/(1+B131)</f>
+        <f>(1+Assumptions!$C$80)/(1+B131)</f>
         <v/>
       </c>
       <c r="C138" s="26">
-        <f>(1+Assumptions!$C$81)/(1+C131)</f>
+        <f>(1+Assumptions!$C$80)/(1+C131)</f>
         <v/>
       </c>
       <c r="D138" s="26">
-        <f>(1+Assumptions!$C$81)/(1+D131)</f>
+        <f>(1+Assumptions!$C$80)/(1+D131)</f>
         <v/>
       </c>
     </row>
@@ -5407,15 +5407,15 @@
         </is>
       </c>
       <c r="B139" s="28">
-        <f>1448.550594/(1+B131)*(1-B138^10)/(1-B138)</f>
+        <f>1408.881541/(1+B131)*(1-B138^10)/(1-B138)</f>
         <v/>
       </c>
       <c r="C139" s="28">
-        <f>1448.550594/(1+C131)*(1-C138^10)/(1-C138)</f>
+        <f>1408.881541/(1+C131)*(1-C138^10)/(1-C138)</f>
         <v/>
       </c>
       <c r="D139" s="28">
-        <f>1448.550594/(1+D131)*(1-D138^10)/(1-D138)</f>
+        <f>1408.881541/(1+D131)*(1-D138^10)/(1-D138)</f>
         <v/>
       </c>
     </row>
@@ -5426,15 +5426,15 @@
         </is>
       </c>
       <c r="B140" s="28">
-        <f>1870.515870*(1+Assumptions!$C$82)/((B131-Assumptions!$C$82)*(1+B131)^10)</f>
+        <f>1820.231542*(1+Assumptions!$C$81)/((B131-Assumptions!$C$81)*(1+B131)^10)</f>
         <v/>
       </c>
       <c r="C140" s="28">
-        <f>1870.515870*(1+Assumptions!$C$82)/((C131-Assumptions!$C$82)*(1+C131)^10)</f>
+        <f>1820.231542*(1+Assumptions!$C$81)/((C131-Assumptions!$C$81)*(1+C131)^10)</f>
         <v/>
       </c>
       <c r="D140" s="28">
-        <f>1870.515870*(1+Assumptions!$C$82)/((D131-Assumptions!$C$82)*(1+D131)^10)</f>
+        <f>1820.231542*(1+Assumptions!$C$81)/((D131-Assumptions!$C$81)*(1+D131)^10)</f>
         <v/>
       </c>
     </row>
@@ -5502,15 +5502,15 @@
         </is>
       </c>
       <c r="B144" s="34">
-        <f>(B143-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(B143-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="C144" s="34">
-        <f>(C143-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(C143-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D144" s="34">
-        <f>(D143-DCF!$C$53+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+        <f>(D143-DCF!$C$53+Assumptions!$C$89+Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5671,27 +5671,27 @@
         </is>
       </c>
       <c r="D6" s="9">
-        <f>Assumptions!$C$97/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>Assumptions!$C$97/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>Assumptions!$C$97/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="G6" s="9">
-        <f>Assumptions!$C$97/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="H6" s="9">
-        <f>Assumptions!$C$97/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="I6" s="9">
-        <f>Assumptions!$C$97/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5712,27 +5712,27 @@
         </is>
       </c>
       <c r="D7" s="39">
-        <f>'Income Statement'!D18/Assumptions!$C$97</f>
+        <f>'Income Statement'!D18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="E7" s="39">
-        <f>'Income Statement'!E18/Assumptions!$C$97</f>
+        <f>'Income Statement'!E18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="F7" s="39">
-        <f>'Income Statement'!F18/Assumptions!$C$97</f>
+        <f>'Income Statement'!F18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="G7" s="39">
-        <f>'Income Statement'!G18/Assumptions!$C$97</f>
+        <f>'Income Statement'!G18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="H7" s="39">
-        <f>'Income Statement'!H18/Assumptions!$C$97</f>
+        <f>'Income Statement'!H18/Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="I7" s="39">
-        <f>'Income Statement'!I18/Assumptions!$C$97</f>
+        <f>'Income Statement'!I18/Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -6118,27 +6118,27 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <f>Assumptions!$C$97/'Income Statement'!D18</f>
+        <f>Assumptions!$C$96/'Income Statement'!D18</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>Assumptions!$C$97/'Income Statement'!E18</f>
+        <f>Assumptions!$C$96/'Income Statement'!E18</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>Assumptions!$C$97/'Income Statement'!F18</f>
+        <f>Assumptions!$C$96/'Income Statement'!F18</f>
         <v/>
       </c>
       <c r="G17" s="10">
-        <f>Assumptions!$C$97/'Income Statement'!G18</f>
+        <f>Assumptions!$C$96/'Income Statement'!G18</f>
         <v/>
       </c>
       <c r="H17" s="10">
-        <f>Assumptions!$C$97/'Income Statement'!H18</f>
+        <f>Assumptions!$C$96/'Income Statement'!H18</f>
         <v/>
       </c>
       <c r="I17" s="10">
-        <f>Assumptions!$C$97/'Income Statement'!I18</f>
+        <f>Assumptions!$C$96/'Income Statement'!I18</f>
         <v/>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="B10" s="38">
-        <f>Assumptions!$C$100</f>
+        <f>Assumptions!$C$99</f>
         <v/>
       </c>
       <c r="C10" s="38">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="B11" s="38">
-        <f>Assumptions!$C$101</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="C11" s="38">
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="B12" s="38">
-        <f>Assumptions!$C$102</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
       <c r="C12" s="38">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>Assumptions!$C$97/Assumptions!$C$6/Assumptions!$C$5</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
         <v/>
       </c>
       <c r="C5" s="8">
-        <f>Assumptions!$C$103</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="D5" s="9">
@@ -6487,7 +6487,7 @@
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>Assumptions!$C$104</f>
+        <f>Assumptions!$C$103</f>
         <v/>
       </c>
       <c r="D6" s="9">
@@ -6510,7 +6510,7 @@
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>Assumptions!$C$105</f>
+        <f>Assumptions!$C$104</f>
         <v/>
       </c>
       <c r="D7" s="9">
@@ -6533,7 +6533,7 @@
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>Assumptions!$C$106</f>
+        <f>Assumptions!$C$105</f>
         <v/>
       </c>
       <c r="D8" s="9">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>Assumptions!$C$103*Sensitivity!C50+Assumptions!$C$104*B6+Assumptions!$C$105*B7+Assumptions!$C$106*B8</f>
+        <f>Assumptions!$C$102*Sensitivity!C50+Assumptions!$C$103*B6+Assumptions!$C$104*B7+Assumptions!$C$105*B8</f>
         <v/>
       </c>
       <c r="E10" s="10">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>Assumptions!$C$103*'SOTP Bridge'!D14+Assumptions!$C$104*B6+Assumptions!$C$105*'Relative &amp; Normalized'!C34+Assumptions!$C$106*'Relative &amp; Normalized'!C41</f>
+        <f>Assumptions!$C$102*'SOTP Bridge'!D14+Assumptions!$C$103*B6+Assumptions!$C$104*'Relative &amp; Normalized'!C34+Assumptions!$C$105*'Relative &amp; Normalized'!C41</f>
         <v/>
       </c>
       <c r="E11" s="10">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>Assumptions!$C$103*Sensitivity!C72+Assumptions!$C$104*B6+Assumptions!$C$105*'Relative &amp; Normalized'!C34+Assumptions!$C$106*'Relative &amp; Normalized'!C41</f>
+        <f>Assumptions!$C$102*Sensitivity!C72+Assumptions!$C$103*B6+Assumptions!$C$104*'Relative &amp; Normalized'!C34+Assumptions!$C$105*'Relative &amp; Normalized'!C41</f>
         <v/>
       </c>
       <c r="E12" s="10">
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>Assumptions!$C$107</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="B34" s="8">
-        <f>Assumptions!$C$81</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="B35" s="8">
-        <f>Assumptions!$C$82</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="C24" s="7">
-        <f>Assumptions!$C$107</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -8285,372 +8285,367 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Average age of the base, MEASURED from notes 5, 6 and 7 (years)</t>
+          <t>Weighted asset life, DERIVED from notes 5, 6 and 7 (years)</t>
         </is>
       </c>
       <c r="C78" s="25" t="n">
-        <v>10.28935645372001</v>
+        <v>28.09842122488282</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Audited consolidated financial statements for the year ended 31 December 2025, signed 9 February 2026, obtained from the company's own investor-relations page, notes 5, 6 and 7. THE AVERAGE AGE OF THE BASE, MEASURED rather than assumed: accumulated depreciation over the year's own charge is, under the straight-line method these accounts use, exactly the charge-weighted average age of the assets bearing that charge — an identity, not an estimate. The property note prints its accumulated column (3,734,337); neither the right-of-use nor the intangible note does, so both are recovered by the identity gross less net (22,649 less 1,878; 364,710 less 315,668) and LABELLED as derived. The three sum to 3,804,150 over a charge of 369,717 = 10.29 years. THIS BASE IS YOUNGER THAN UNIFORM — half the 28.10-year life would put it at 14.05 — so escalating the book charge over half the life OVERSTATES what replacement costs, by 7.2% at this market's 2% terminal. The distinction matters because the escalation is over the AGE of the assets, and half the life is that age only where vintages are uniform, which here they are not (2026-09-04)</t>
+          <t>Audited consolidated financial statements for the year ended 31 December 2025, signed 9 February 2026, obtained from the company's own investor-relations page, notes 5, 6 and 7, DERIVED BY IDENTITY from those notes' own cost and charge columns and LABELLED as derived, and READ BY OCR OFF THE RENDERED PIXELS because the filing carries no usable text layer (85 bytes across 85 pages) and its property note is printed landscape, so the page was rotated before it could be read. ARITHMETIC IS THE ARBITER AND THE EXTRACTION FOOTS FOUR WAYS: the cost columns sum to the printed total of 10,929,327; the accumulated-depreciation columns to 3,734,337; cost less accumulated reproduces the balance sheet's 7,194,990; and the year's charge of 352,199 splits to the 341,696 in cost of sales and 10,503 in general and administrative expenses the notes state separately. Property, plant and equipment 10,001,105 (total less land, which is never depreciated, and less capital work in progress, whose accumulated column is impairment rather than depreciation) over 352,199 gives 28.40 years; right-of-use 22,649 over 5,361 gives 4.22; intangibles are DISCLOSED at 30 years outright and their gross cost follows from the flat charge. Blended, 28.10 years, cross-checked at 27.88 on FY2024's own columns. The right-of-use figure does NOT match the 15-year equipment lease the note names, and the note explains why rather than contradicting it: the book is 19,997 of buildings against 2,652 of equipment, and the buildings are a head office and labour accommodation on ONE-YEAR terms (2026-02-09)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Weighted asset life, DERIVED from notes 5, 6 and 7 (years)</t>
+          <t>Invested capital per unit of real growth (AED mn)</t>
         </is>
       </c>
       <c r="C79" s="25" t="n">
-        <v>28.09842122488282</v>
+        <v>5526.341086457007</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Audited consolidated financial statements for the year ended 31 December 2025, signed 9 February 2026, obtained from the company's own investor-relations page, notes 5, 6 and 7, DERIVED BY IDENTITY from those notes' own cost and charge columns and LABELLED as derived, and READ BY OCR OFF THE RENDERED PIXELS because the filing carries no usable text layer (85 bytes across 85 pages) and its property note is printed landscape, so the page was rotated before it could be read. ARITHMETIC IS THE ARBITER AND THE EXTRACTION FOOTS FOUR WAYS: the cost columns sum to the printed total of 10,929,327; the accumulated-depreciation columns to 3,734,337; cost less accumulated reproduces the balance sheet's 7,194,990; and the year's charge of 352,199 splits to the 341,696 in cost of sales and 10,503 in general and administrative expenses the notes state separately. Property, plant and equipment 10,001,105 (total less land, which is never depreciated, and less capital work in progress, whose accumulated column is impairment rather than depreciation) over 352,199 gives 28.40 years; right-of-use 22,649 over 5,361 gives 4.22; intangibles are DISCLOSED at 30 years outright and their gross cost follows from the flat charge. Blended, 28.10 years, cross-checked at 27.88 on FY2024's own columns. The right-of-use figure does NOT match the 15-year equipment lease the note names, and the note explains why rather than contradicting it: the book is 19,997 of buildings against 2,652 of equipment, and the buildings are a head office and labour accommodation on ONE-YEAR terms (2026-02-09)</t>
+          <t>One per cent of real growth costs one per cent of the invested capital the business operates on. The marginal reading across the explicit window is NEGATIVE here, because the plant is written down faster than capex replaces it over those five years, and a negative capital requirement would credit this company for growing</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Invested capital per unit of real growth (AED mn)</t>
-        </is>
-      </c>
-      <c r="C80" s="25" t="n">
-        <v>5526.341086457007</v>
+          <t>Growth, FY2031-FY2040 window — (1+inflation)(1+real)-1</t>
+        </is>
+      </c>
+      <c r="C80" s="10">
+        <f>(1+$C$75)*(1+$C$76)-1</f>
+        <v/>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>One per cent of real growth costs one per cent of the invested capital the business operates on. The marginal reading across the explicit window is NEGATIVE here, because the plant is written down faster than capex replaces it over those five years, and a negative capital requirement would credit this company for growing</t>
+          <t>DERIVED from the two rows above, never typed. It reproduces the previous edition's 2.50% to the basis point, because under a tariff the regulator does not index a nominal growth rate IS a volume assumption</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Growth, FY2031-FY2040 window — (1+inflation)(1+real)-1</t>
+          <t>Growth beyond FY2040 — the same identity on the stage-two real rate</t>
         </is>
       </c>
       <c r="C81" s="10">
-        <f>(1+$C$75)*(1+$C$76)-1</f>
+        <f>(1+$C$75)*(1+$C$77)-1</f>
         <v/>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>DERIVED from the two rows above, never typed. It reproduces the previous edition's 2.50% to the basis point, because under a tariff the regulator does not index a nominal growth rate IS a volume assumption</t>
+          <t>DERIVED. Reproduces the previous edition's 1.50%, and makes visible that it is a real DECLINE of half a point a year</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Growth beyond FY2040 — the same identity on the stage-two real rate</t>
-        </is>
-      </c>
-      <c r="C82" s="10">
-        <f>(1+$C$75)*(1+$C$77)-1</f>
-        <v/>
+          <t>Stub period — 30-Jun-2026 anchor to end-FY2026 (years)</t>
+        </is>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>0.4999999999999997</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>DERIVED. Reproduces the previous edition's 1.50%, and makes visible that it is a real DECLINE of half a point a year</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>Stub period — 30-Jun-2026 anchor to end-FY2026 (years)</t>
-        </is>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.4999999999999997</v>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
           <t>The bridge is struck on the 30-Jun-2026 reviewed balance sheet, so the cash-flow clock starts there too: FY2026 contributes its second half only and later year-ends sit at 1.5 to 4.5 years</t>
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>Bridge — 30-Jun-2026 reviewed balance sheet</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="n"/>
+      <c r="C84" s="14" t="n"/>
+      <c r="D84" s="14" t="n"/>
+      <c r="E84" s="14" t="n"/>
+      <c r="F84" s="14" t="n"/>
+      <c r="G84" s="14" t="n"/>
+      <c r="H84" s="14" t="n"/>
+    </row>
     <row r="85">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>Bridge — 30-Jun-2026 reviewed balance sheet</t>
-        </is>
-      </c>
-      <c r="B85" s="14" t="n"/>
-      <c r="C85" s="14" t="n"/>
-      <c r="D85" s="14" t="n"/>
-      <c r="E85" s="14" t="n"/>
-      <c r="F85" s="14" t="n"/>
-      <c r="G85" s="14" t="n"/>
-      <c r="H85" s="14" t="n"/>
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Bank borrowings (AED mn)</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="n">
+        <v>5502.845</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Bank borrowings 30-Jun-2026: current 2.845 + non-current 5,500.000, reviewed interim BS (2026-08-05)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>Bank borrowings (AED mn)</t>
+          <t>Lease liabilities (AED mn)</t>
         </is>
       </c>
       <c r="C86" s="25" t="n">
-        <v>5502.845</v>
+        <v>0.872</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Bank borrowings 30-Jun-2026: current 2.845 + non-current 5,500.000, reviewed interim BS (2026-08-05)</t>
+          <t>Lease liabilities 30-Jun-2026 (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities (AED mn)</t>
+          <t>Cash and cash equivalents (AED mn)</t>
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>0.872</v>
+        <v>2472.012</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Lease liabilities 30-Jun-2026 (2026-08-05)</t>
+          <t>Cash and cash equivalents 30-Jun-2026 (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents (AED mn)</t>
+          <t>Term deposits (AED mn)</t>
         </is>
       </c>
       <c r="C88" s="25" t="n">
-        <v>2472.012</v>
+        <v>40.212</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents 30-Jun-2026 (2026-08-05)</t>
+          <t>Term deposits (&gt;3m) 30-Jun-2026 (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Term deposits (AED mn)</t>
+          <t>Related-party acquisition receivables at book (Note 8: 1,005.0 Dubai Aviation City + 289.4 Nakheel) (AED mn)</t>
         </is>
       </c>
       <c r="C89" s="25" t="n">
-        <v>40.212</v>
+        <v>1294.442</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Term deposits (&gt;3m) 30-Jun-2026 (2026-08-05)</t>
+          <t>Financial assets at amortised cost, 30-Jun-2026 reviewed BS: non-current 1,273.130 + current 21.312. Note 8 composition: AED 1,005.030 from Dubai Aviation City Corporation (DXB CoolCo acquisition, 2023) + AED 289.412 from Nakheel PJSC (Empower Snow acquisition, 2021) — related-party acquisition receivables under common control, NOT an operating concession asset. Clean financial-asset treatment adopted per critique (17-Aug-2026): interest income excluded from operating EBITDA/FCFF, asset added at book in the EV-to-equity bridge, and excluded from terminal invested capital (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Related-party acquisition receivables at book (Note 8: 1,005.0 Dubai Aviation City + 289.4 Nakheel) (AED mn)</t>
+          <t>Investment properties (AED mn)</t>
         </is>
       </c>
       <c r="C90" s="25" t="n">
-        <v>1294.442</v>
+        <v>168.716</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Financial assets at amortised cost, 30-Jun-2026 reviewed BS: non-current 1,273.130 + current 21.312. Note 8 composition: AED 1,005.030 from Dubai Aviation City Corporation (DXB CoolCo acquisition, 2023) + AED 289.412 from Nakheel PJSC (Empower Snow acquisition, 2021) — related-party acquisition receivables under common control, NOT an operating concession asset. Clean financial-asset treatment adopted per critique (17-Aug-2026): interest income excluded from operating EBITDA/FCFF, asset added at book in the EV-to-equity bridge, and excluded from terminal invested capital (2026-08-05)</t>
+          <t>Investment properties 30-Jun-2026 (non-operating side pocket, added in the bridge at book) (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Investment properties (AED mn)</t>
+          <t>Financial assets at fair value through profit or loss (AED mn)</t>
         </is>
       </c>
       <c r="C91" s="25" t="n">
-        <v>168.716</v>
+        <v>53.411</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Investment properties 30-Jun-2026 (non-operating side pocket, added in the bridge at book) (2026-08-05)</t>
+          <t>Financial assets at FVTPL 30-Jun-2026 (cash-like, added in the bridge) (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at fair value through profit or loss (AED mn)</t>
+          <t>Financial assets at fair value through OCI (AED mn)</t>
         </is>
       </c>
       <c r="C92" s="25" t="n">
-        <v>53.411</v>
+        <v>74.56399999999999</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Financial assets at FVTPL 30-Jun-2026 (cash-like, added in the bridge) (2026-08-05)</t>
+          <t>Financial assets at FVOCI 30-Jun-2026 (added at book) (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at fair value through OCI (AED mn)</t>
+          <t>Equity attributable to shareholders, 30-Jun-2026 (AED mn)</t>
         </is>
       </c>
       <c r="C93" s="25" t="n">
-        <v>74.56399999999999</v>
+        <v>3337.585</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Financial assets at FVOCI 30-Jun-2026 (added at book) (2026-08-05)</t>
+          <t>Equity attributable to holders, 30-Jun-2026 reviewed BS (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to shareholders, 30-Jun-2026 (AED mn)</t>
+          <t>Non-controlling interests, 30-Jun-2026 (AED mn)</t>
         </is>
       </c>
       <c r="C94" s="25" t="n">
-        <v>3337.585</v>
+        <v>190.745</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Equity attributable to holders, 30-Jun-2026 reviewed BS (2026-08-05)</t>
+          <t>Non-controlling interests (15% of DXB CoolCo et al. — the H1-2026 subsidiary note shows Dxb CoolCo FZCO at 85%/85%), 30-Jun-2026 reviewed BS (2026-08-05)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests, 30-Jun-2026 (AED mn)</t>
-        </is>
-      </c>
-      <c r="C95" s="25" t="n">
-        <v>190.745</v>
+          <t>Yield earned on cash balances</t>
+        </is>
+      </c>
+      <c r="C95" s="30" t="n">
+        <v>0.03500000000000009</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests (15% of DXB CoolCo et al. — the H1-2026 subsidiary note shows Dxb CoolCo FZCO at 85%/85%), 30-Jun-2026 reviewed BS (2026-08-05)</t>
+          <t>Deposit-rate assumption used in the forecast finance line; flagged as an estimate</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Yield earned on cash balances</t>
-        </is>
-      </c>
-      <c r="C96" s="30" t="n">
-        <v>0.03500000000000009</v>
+          <t>Committed annual dividend (AED mn)</t>
+        </is>
+      </c>
+      <c r="C96" s="25" t="n">
+        <v>875</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Deposit-rate assumption used in the forecast finance line; flagged as an estimate</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Committed annual dividend (AED mn)</t>
-        </is>
-      </c>
-      <c r="C97" s="25" t="n">
-        <v>875</v>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
           <t>Dividend AED 875m/yr committed for 2025 AND 2026 (2 x 437.5m, Oct/Apr), deck p12; FY2025 FS note 39: 875.0 paid in 2025 (2026-08-05)</t>
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>Valuation lenses</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n"/>
+      <c r="C98" s="14" t="n"/>
+      <c r="D98" s="14" t="n"/>
+      <c r="E98" s="14" t="n"/>
+      <c r="F98" s="14" t="n"/>
+      <c r="G98" s="14" t="n"/>
+      <c r="H98" s="14" t="n"/>
+    </row>
     <row r="99">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>Valuation lenses</t>
-        </is>
-      </c>
-      <c r="B99" s="14" t="n"/>
-      <c r="C99" s="14" t="n"/>
-      <c r="D99" s="14" t="n"/>
-      <c r="E99" s="14" t="n"/>
-      <c r="F99" s="14" t="n"/>
-      <c r="G99" s="14" t="n"/>
-      <c r="H99" s="14" t="n"/>
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Peer EV/EBITDA — Tabreed (trailing, restruck at the anchor)</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Tabreed (DFM) FY2025 results at the 2026-08-07 anchor (restruck: Tabreed 2.46 on 6/7-Aug; 0.5x of multiple = AED 0.078/share on this lens)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Peer EV/EBITDA — Tabreed (trailing, restruck at the anchor)</t>
+          <t>Peer price/earnings — Tabreed (trailing, restruck at the anchor)</t>
         </is>
       </c>
       <c r="C100" s="32" t="n">
-        <v>10.1</v>
+        <v>15</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Tabreed (DFM) FY2025 results at the 2026-08-07 anchor (restruck: Tabreed 2.46 on 6/7-Aug; 0.5x of multiple = AED 0.078/share on this lens)</t>
+          <t>Tabreed (DFM), close 2.46 on 6/7-Aug-2026 — cross-check input only</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>Peer price/earnings — Tabreed (trailing, restruck at the anchor)</t>
+          <t>Peer price/earnings — DEWA (parent)</t>
         </is>
       </c>
       <c r="C101" s="32" t="n">
-        <v>15</v>
+        <v>16.8</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Tabreed (DFM), close 2.46 on 6/7-Aug-2026 — cross-check input only</t>
+          <t>DEWA (DFM), Aug-2026 — context only, majority owner</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>Peer price/earnings — DEWA (parent)</t>
-        </is>
-      </c>
-      <c r="C102" s="32" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>DEWA (DFM), Aug-2026 — context only, majority owner</t>
-        </is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
+          <t>Weight — relative multiples</t>
         </is>
       </c>
       <c r="C103" s="24" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative multiples</t>
+          <t>Weight — normalised earnings</t>
         </is>
       </c>
       <c r="C104" s="24" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised earnings</t>
+          <t>Weight — book value</t>
         </is>
       </c>
       <c r="C105" s="24" t="n">
@@ -8660,23 +8655,13 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>Weight — book value</t>
-        </is>
-      </c>
-      <c r="C106" s="24" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
           <t>DEWA control-transaction price, Feb-2026 (AED)</t>
         </is>
       </c>
-      <c r="C107" s="22" t="n">
+      <c r="C106" s="22" t="n">
         <v>2.16</v>
       </c>
-      <c r="H107" s="4" t="inlineStr">
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>Related-party CONTROL price for Dubai Holding's 24% stake — a disclosed reference point, never fair value</t>
         </is>
@@ -8791,15 +8776,15 @@
         </is>
       </c>
       <c r="C7" s="19">
-        <f>Assumptions!$C$90</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="D7" s="19">
-        <f>Assumptions!$C$90</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="E7" s="19">
-        <f>Assumptions!$C$90</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -8810,15 +8795,15 @@
         </is>
       </c>
       <c r="C8" s="19">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="D8" s="19">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="E8" s="19">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -8829,15 +8814,15 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$C$92</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
       <c r="D9" s="19">
-        <f>Assumptions!$C$92</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
       <c r="E9" s="19">
-        <f>Assumptions!$C$92</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
     </row>
@@ -8848,15 +8833,15 @@
         </is>
       </c>
       <c r="C10" s="19">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="D10" s="19">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="E10" s="19">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -9780,7 +9765,7 @@
         </is>
       </c>
       <c r="C6" s="38">
-        <f>Assumptions!$C$100</f>
+        <f>Assumptions!$C$99</f>
         <v/>
       </c>
     </row>
@@ -9813,7 +9798,7 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$C$90</f>
+        <f>Assumptions!$C$89</f>
         <v/>
       </c>
     </row>
@@ -9824,7 +9809,7 @@
         </is>
       </c>
       <c r="C10" s="19">
-        <f>Assumptions!$C$91+Assumptions!$C$92+Assumptions!$C$93</f>
+        <f>Assumptions!$C$90+Assumptions!$C$91+Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -9869,7 +9854,7 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>Assumptions!$C$101*'Income Statement'!E18/Assumptions!$C$6</f>
+        <f>Assumptions!$C$100*'Income Statement'!E18/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -10027,7 +10012,7 @@
         </is>
       </c>
       <c r="C30" s="38">
-        <f>(1-Assumptions!$C$81/C29)/(DCF!$C$50-Assumptions!$C$81)</f>
+        <f>(1-Assumptions!$C$80/C29)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -10061,7 +10046,7 @@
         </is>
       </c>
       <c r="C33" s="38">
-        <f>(1-Assumptions!$C$81/C32)/(DCF!$C$50-Assumptions!$C$81)</f>
+        <f>(1-Assumptions!$C$80/C32)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -10096,7 +10081,7 @@
         </is>
       </c>
       <c r="C37" s="9">
-        <f>Assumptions!$C$94/Assumptions!$C$6</f>
+        <f>Assumptions!$C$93/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -10107,7 +10092,7 @@
         </is>
       </c>
       <c r="C38" s="38">
-        <f>(C29-Assumptions!$C$81)/(DCF!$C$50-Assumptions!$C$81)</f>
+        <f>(C29-Assumptions!$C$80)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -10130,7 +10115,7 @@
         </is>
       </c>
       <c r="C40" s="38">
-        <f>(C32-Assumptions!$C$81)/(DCF!$C$50-Assumptions!$C$81)</f>
+        <f>(C32-Assumptions!$C$80)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -10165,7 +10150,7 @@
         </is>
       </c>
       <c r="C44" s="9">
-        <f>Assumptions!$C$97/Assumptions!$C$6</f>
+        <f>Assumptions!$C$96/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -10176,7 +10161,7 @@
         </is>
       </c>
       <c r="C45" s="7">
-        <f>C44*(1+Assumptions!$C$81)/(DCF!$C$50-Assumptions!$C$81)</f>
+        <f>C44*(1+Assumptions!$C$80)/(DCF!$C$50-Assumptions!$C$80)</f>
         <v/>
       </c>
     </row>
@@ -10650,7 +10635,7 @@
         </is>
       </c>
       <c r="B19" s="41">
-        <f>Assumptions!$C$83</f>
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C19" s="42">
@@ -10704,7 +10689,7 @@
         </is>
       </c>
       <c r="B21" s="43">
-        <f>B18*B20*Assumptions!$C$83</f>
+        <f>B18*B20*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C21" s="43">
@@ -10778,7 +10763,7 @@
         </is>
       </c>
       <c r="C27" s="8">
-        <f>Assumptions!$C$81</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -10800,7 +10785,7 @@
         </is>
       </c>
       <c r="C29" s="8">
-        <f>Assumptions!$C$82</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -11071,7 +11056,7 @@
         </is>
       </c>
       <c r="C53" s="19">
-        <f>Assumptions!$C$86+Assumptions!$C$87-Assumptions!$C$88-Assumptions!$C$89</f>
+        <f>Assumptions!$C$85+Assumptions!$C$86-Assumptions!$C$87-Assumptions!$C$88</f>
         <v/>
       </c>
     </row>
@@ -11206,7 +11191,7 @@
         </is>
       </c>
       <c r="B64" s="28">
-        <f>B63*B20*Assumptions!$C$83</f>
+        <f>B63*B20*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C64" s="28">
@@ -11361,7 +11346,7 @@
         </is>
       </c>
       <c r="B78" s="28">
-        <f>B18/(1+$D$56)^B19*Assumptions!$C$83</f>
+        <f>B18/(1+$D$56)^B19*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C78" s="28">
@@ -11410,7 +11395,7 @@
         </is>
       </c>
       <c r="C81" s="28">
-        <f>1448.550594</f>
+        <f>1408.881541</f>
         <v/>
       </c>
     </row>
@@ -11432,7 +11417,7 @@
         </is>
       </c>
       <c r="C83" s="28">
-        <f>1870.515870*(1+C29)/(($D$56-C29)*(1+$D$56)^10)</f>
+        <f>1820.231542*(1+C29)/(($D$56-C29)*(1+$D$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -11536,7 +11521,7 @@
         </is>
       </c>
       <c r="B91" s="27">
-        <f>(C52*C50+(Assumptions!$C$86+Assumptions!$C$87)*C51*(1-Assumptions!$C$7))/(C52+Assumptions!$C$86+Assumptions!$C$87)</f>
+        <f>(C52*C50+(Assumptions!$C$85+Assumptions!$C$86)*C51*(1-Assumptions!$C$7))/(C52+Assumptions!$C$85+Assumptions!$C$86)</f>
         <v/>
       </c>
       <c r="C91" s="7">
@@ -11556,7 +11541,7 @@
         </is>
       </c>
       <c r="B92" s="27">
-        <f>C55*C50+C54*(((Assumptions!$C$86+Assumptions!$C$87)*C51*(1-Assumptions!$C$7)-(Assumptions!$C$88+Assumptions!$C$89)*Assumptions!$C$96*(1-Assumptions!$C$7))/C53)</f>
+        <f>C55*C50+C54*(((Assumptions!$C$85+Assumptions!$C$86)*C51*(1-Assumptions!$C$7)-(Assumptions!$C$87+Assumptions!$C$88)*Assumptions!$C$95*(1-Assumptions!$C$7))/C53)</f>
         <v/>
       </c>
       <c r="C92" s="7">
@@ -11622,15 +11607,15 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Stage one, FY2031 — less capital maintenance at replacement cost, that charge escalated over the MEASURED age of the base</t>
+          <t>Stage one, FY2031 — less capital maintenance at replacement cost, that charge escalated over half the derived life</t>
         </is>
       </c>
       <c r="C96" s="28">
-        <f>-C95*(1+Assumptions!$C$75)^Assumptions!$C$78</f>
+        <f>-C95*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
         <v/>
       </c>
       <c r="G96" s="28">
-        <f>-G95*(1+Assumptions!$C$75)^Assumptions!$C$78</f>
+        <f>-G95*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
         <v/>
       </c>
     </row>
@@ -11712,15 +11697,15 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Stage two, FY2041 — less capital maintenance at replacement cost, that charge escalated over the MEASURED age of the base</t>
+          <t>Stage two, FY2041 — less capital maintenance at replacement cost, that charge escalated over half the derived life</t>
         </is>
       </c>
       <c r="C105" s="28">
-        <f>-C104*(1+Assumptions!$C$75)^Assumptions!$C$78</f>
+        <f>-C104*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
         <v/>
       </c>
       <c r="G105" s="28">
-        <f>-G104*(1+Assumptions!$C$75)^Assumptions!$C$78</f>
+        <f>-G104*(1+Assumptions!$C$75)^(Assumptions!$C$78/2)</f>
         <v/>
       </c>
     </row>
@@ -12200,23 +12185,23 @@
         <v/>
       </c>
       <c r="E13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*Assumptions!$C$88)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*Assumptions!$C$87)</f>
         <v/>
       </c>
       <c r="F13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*'Balance Sheet'!E9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!E9)</f>
         <v/>
       </c>
       <c r="G13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*'Balance Sheet'!F9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!F9)</f>
         <v/>
       </c>
       <c r="H13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*'Balance Sheet'!G9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!G9)</f>
         <v/>
       </c>
       <c r="I13" s="28">
-        <f>-(Assumptions!$C$74*Assumptions!$C$86-Assumptions!$C$96*'Balance Sheet'!H9)</f>
+        <f>-(Assumptions!$C$74*Assumptions!$C$85-Assumptions!$C$95*'Balance Sheet'!H9)</f>
         <v/>
       </c>
     </row>

--- a/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
+++ b/engine/empower_study/EMPOWER_Valuation_Model_09082026_public.xlsx
@@ -3805,23 +3805,23 @@
         </is>
       </c>
       <c r="B42" s="28">
-        <f>1351.086349</f>
+        <f>1317.457139</f>
         <v/>
       </c>
       <c r="C42" s="28">
-        <f>1374.204426</f>
+        <f>1340.017422</f>
         <v/>
       </c>
       <c r="D42" s="28">
-        <f>1391.542984</f>
+        <f>1356.937635</f>
         <v/>
       </c>
       <c r="E42" s="28">
-        <f>1408.881541</f>
+        <f>1373.857848</f>
         <v/>
       </c>
       <c r="F42" s="28">
-        <f>1426.220099</f>
+        <f>1390.778060</f>
         <v/>
       </c>
     </row>
@@ -3886,23 +3886,23 @@
         </is>
       </c>
       <c r="B45" s="28">
-        <f>1747.758253</f>
+        <f>1721.929313</f>
         <v/>
       </c>
       <c r="C45" s="28">
-        <f>1776.747568</f>
+        <f>1750.490215</f>
         <v/>
       </c>
       <c r="D45" s="28">
-        <f>1798.489555</f>
+        <f>1771.910892</f>
         <v/>
       </c>
       <c r="E45" s="28">
-        <f>1820.231542</f>
+        <f>1793.331568</f>
         <v/>
       </c>
       <c r="F45" s="28">
-        <f>1841.973528</f>
+        <f>1814.752245</f>
         <v/>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="C65" s="28">
-        <f>1275.872653</f>
+        <f>1244.083985</f>
         <v/>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="C67" s="28">
-        <f>1652.102614</f>
+        <f>1627.687305</f>
         <v/>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="C94" s="28">
-        <f>1086.112904</f>
+        <f>1059.038517</f>
         <v/>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C97" s="28">
-        <f>1407.094633</f>
+        <f>1386.300131</f>
         <v/>
       </c>
     </row>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="C119" s="28">
-        <f>1443.493007</f>
+        <f>1407.605923</f>
         <v/>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="C122" s="28">
-        <f>1865.103177</f>
+        <f>1837.540076</f>
         <v/>
       </c>
     </row>
@@ -5407,15 +5407,15 @@
         </is>
       </c>
       <c r="B139" s="28">
-        <f>1408.881541/(1+B131)*(1-B138^10)/(1-B138)</f>
+        <f>1373.857848/(1+B131)*(1-B138^10)/(1-B138)</f>
         <v/>
       </c>
       <c r="C139" s="28">
-        <f>1408.881541/(1+C131)*(1-C138^10)/(1-C138)</f>
+        <f>1373.857848/(1+C131)*(1-C138^10)/(1-C138)</f>
         <v/>
       </c>
       <c r="D139" s="28">
-        <f>1408.881541/(1+D131)*(1-D138^10)/(1-D138)</f>
+        <f>1373.857848/(1+D131)*(1-D138^10)/(1-D138)</f>
         <v/>
       </c>
     </row>
@@ -5426,15 +5426,15 @@
         </is>
       </c>
       <c r="B140" s="28">
-        <f>1820.231542*(1+Assumptions!$C$81)/((B131-Assumptions!$C$81)*(1+B131)^10)</f>
+        <f>1793.331568*(1+Assumptions!$C$81)/((B131-Assumptions!$C$81)*(1+B131)^10)</f>
         <v/>
       </c>
       <c r="C140" s="28">
-        <f>1820.231542*(1+Assumptions!$C$81)/((C131-Assumptions!$C$81)*(1+C131)^10)</f>
+        <f>1793.331568*(1+Assumptions!$C$81)/((C131-Assumptions!$C$81)*(1+C131)^10)</f>
         <v/>
       </c>
       <c r="D140" s="28">
-        <f>1820.231542*(1+Assumptions!$C$81)/((D131-Assumptions!$C$81)*(1+D131)^10)</f>
+        <f>1793.331568*(1+Assumptions!$C$81)/((D131-Assumptions!$C$81)*(1+D131)^10)</f>
         <v/>
       </c>
     </row>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="C81" s="28">
-        <f>1408.881541</f>
+        <f>1373.857848</f>
         <v/>
       </c>
     </row>
@@ -11417,7 +11417,7 @@
         </is>
       </c>
       <c r="C83" s="28">
-        <f>1820.231542*(1+C29)/(($D$56-C29)*(1+$D$56)^10)</f>
+        <f>1793.331568*(1+C29)/(($D$56-C29)*(1+$D$56)^10)</f>
         <v/>
       </c>
     </row>
@@ -11577,30 +11577,30 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Stage one, FY2031 — operating profit after tax, grown one year</t>
+          <t>Stage one, FY2031 — operating profit after tax (the stage grows this once)</t>
         </is>
       </c>
       <c r="C94" s="28">
-        <f>1486.936920*(1+0.0250000000)</f>
+        <f>1486.936920</f>
         <v/>
       </c>
       <c r="G94" s="28">
-        <f>1388.897123*(1+0.0250000000)</f>
+        <f>1388.897123</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Stage one, FY2031 — plus the book depreciation and amortisation charge, grown</t>
+          <t>Stage one, FY2031 — plus the book depreciation and amortisation charge</t>
         </is>
       </c>
       <c r="C95" s="28">
-        <f>408.390760*(1+0.0250000000)</f>
+        <f>408.390760</f>
         <v/>
       </c>
       <c r="G95" s="28">
-        <f>408.390760*(1+0.0250000000)</f>
+        <f>408.390760</f>
         <v/>
       </c>
     </row>
@@ -11641,11 +11641,11 @@
         </is>
       </c>
       <c r="C98" s="28">
-        <f>-Assumptions!$C$75*-2250.419341*(1+0.0250000000)</f>
+        <f>-Assumptions!$C$75*-2250.419341</f>
         <v/>
       </c>
       <c r="G98" s="28">
-        <f>-Assumptions!$C$75*-2250.419341*(1+0.0250000000)</f>
+        <f>-Assumptions!$C$75*-2250.419341</f>
         <v/>
       </c>
     </row>
@@ -11667,30 +11667,30 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Stage two, FY2041 — operating profit after tax, grown one year</t>
+          <t>Stage two, FY2041 — operating profit after tax (the stage grows this once)</t>
         </is>
       </c>
       <c r="C103" s="28">
-        <f>1903.404970*(1+0.0150000000)</f>
+        <f>1903.404970</f>
         <v/>
       </c>
       <c r="G103" s="28">
-        <f>1777.905741*(1+0.0150000000)</f>
+        <f>1777.905741</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Stage two, FY2041 — plus the book depreciation and amortisation charge, grown</t>
+          <t>Stage two, FY2041 — plus the book depreciation and amortisation charge</t>
         </is>
       </c>
       <c r="C104" s="28">
-        <f>522.774699*(1+0.0150000000)</f>
+        <f>522.774699</f>
         <v/>
       </c>
       <c r="G104" s="28">
-        <f>522.774699*(1+0.0150000000)</f>
+        <f>522.774699</f>
         <v/>
       </c>
     </row>
@@ -11731,11 +11731,11 @@
         </is>
       </c>
       <c r="C107" s="28">
-        <f>-Assumptions!$C$75*-2880.727016*(1+0.0150000000)</f>
+        <f>-Assumptions!$C$75*-2880.727016</f>
         <v/>
       </c>
       <c r="G107" s="28">
-        <f>-Assumptions!$C$75*-2880.727016*(1+0.0150000000)</f>
+        <f>-Assumptions!$C$75*-2880.727016</f>
         <v/>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
         </is>
       </c>
       <c r="C111" s="28">
-        <f>F14*(1+C27)/$C$56</f>
+        <f>F14/$C$56</f>
         <v/>
       </c>
     </row>
